--- a/Beta州_国家分组表.xlsx
+++ b/Beta州_国家分组表.xlsx
@@ -10,7 +10,9 @@
     <sheet name="按大区" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="按国家" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'按大区'!$A$1:$G$741</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -18,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -49,6 +51,10 @@
     <font>
       <name val="Consolas"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <name val="Consolas"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="4">
@@ -128,7 +134,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -160,6 +166,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -527,7 +536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F741"/>
+  <dimension ref="A1:G741"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -536,6 +545,7 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="50" customWidth="1" min="6" max="6"/>
+    <col width="26" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
@@ -569,6 +579,11 @@
           <t>state英文名</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>胜利点</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -597,6 +612,11 @@
       <c r="F2" s="6" t="inlineStr">
         <is>
           <t>Mondstadt</t>
+        </is>
+      </c>
+      <c r="G2" s="13" t="inlineStr">
+        <is>
+          <t>1073(50)</t>
         </is>
       </c>
     </row>
@@ -625,6 +645,11 @@
           <t>West_Wind_Knights</t>
         </is>
       </c>
+      <c r="G3" s="13" t="inlineStr">
+        <is>
+          <t>4364(20)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="7" t="n"/>
@@ -651,6 +676,11 @@
           <t>Outer_City_Mondstadt</t>
         </is>
       </c>
+      <c r="G4" s="13" t="inlineStr">
+        <is>
+          <t>2824(5)</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="7" t="n"/>
@@ -677,6 +707,11 @@
           <t>Windrise</t>
         </is>
       </c>
+      <c r="G5" s="13" t="inlineStr">
+        <is>
+          <t>4540(25)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n"/>
@@ -703,6 +738,11 @@
           <t>Mondstadt_Bridge</t>
         </is>
       </c>
+      <c r="G6" s="13" t="inlineStr">
+        <is>
+          <t>858(25)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n"/>
@@ -729,6 +769,11 @@
           <t>Whispering_Woods</t>
         </is>
       </c>
+      <c r="G7" s="13" t="inlineStr">
+        <is>
+          <t>2074(8)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n"/>
@@ -755,6 +800,11 @@
           <t>Temple_of_Zephyr_Eagle</t>
         </is>
       </c>
+      <c r="G8" s="13" t="inlineStr">
+        <is>
+          <t>63(15)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n"/>
@@ -781,6 +831,11 @@
           <t>Temple_of_North_Wind_Wolf</t>
         </is>
       </c>
+      <c r="G9" s="13" t="inlineStr">
+        <is>
+          <t>2816(15)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n"/>
@@ -807,6 +862,11 @@
           <t>Thousand_Winds_Temple</t>
         </is>
       </c>
+      <c r="G10" s="13" t="inlineStr">
+        <is>
+          <t>4340(50)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n"/>
@@ -833,6 +893,11 @@
           <t>Starsnatch_Cliff</t>
         </is>
       </c>
+      <c r="G11" s="13" t="inlineStr">
+        <is>
+          <t>4231(5)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n"/>
@@ -859,6 +924,11 @@
           <t>Starfell_Lake</t>
         </is>
       </c>
+      <c r="G12" s="13" t="inlineStr">
+        <is>
+          <t>4250(25)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n"/>
@@ -885,6 +955,11 @@
           <t>Stormbearer_Coast</t>
         </is>
       </c>
+      <c r="G13" s="13" t="inlineStr">
+        <is>
+          <t>236(5)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n"/>
@@ -911,6 +986,11 @@
           <t>Falcon_Coast</t>
         </is>
       </c>
+      <c r="G14" s="13" t="inlineStr">
+        <is>
+          <t>4571(5)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n"/>
@@ -937,6 +1017,11 @@
           <t>Stormbearer_Point</t>
         </is>
       </c>
+      <c r="G15" s="13" t="inlineStr">
+        <is>
+          <t>4160(5)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n"/>
@@ -963,6 +1048,11 @@
           <t>Stormbearer_Mountains</t>
         </is>
       </c>
+      <c r="G16" s="13" t="inlineStr">
+        <is>
+          <t>4197(5)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n"/>
@@ -989,6 +1079,11 @@
           <t>Shapeless_Wind</t>
         </is>
       </c>
+      <c r="G17" s="13" t="inlineStr">
+        <is>
+          <t>4121(12)</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n"/>
@@ -1015,6 +1110,11 @@
           <t>Nameless_Island</t>
         </is>
       </c>
+      <c r="G18" s="13" t="inlineStr">
+        <is>
+          <t>4240(20)</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n"/>
@@ -1041,6 +1141,11 @@
           <t>Cider_Lake</t>
         </is>
       </c>
+      <c r="G19" s="13" t="inlineStr">
+        <is>
+          <t>4152(20)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n"/>
@@ -1067,6 +1172,11 @@
           <t>JingFu_Port</t>
         </is>
       </c>
+      <c r="G20" s="13" t="inlineStr">
+        <is>
+          <t>3739(10)</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n"/>
@@ -1093,6 +1203,11 @@
           <t>JingFu_Port</t>
         </is>
       </c>
+      <c r="G21" s="13" t="inlineStr">
+        <is>
+          <t>2883(5)</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n"/>
@@ -1119,6 +1234,11 @@
           <t>Silence_Sea</t>
         </is>
       </c>
+      <c r="G22" s="13" t="inlineStr">
+        <is>
+          <t>1195(10)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n"/>
@@ -1145,6 +1265,11 @@
           <t>Gunnhildr_Castle</t>
         </is>
       </c>
+      <c r="G23" s="13" t="inlineStr">
+        <is>
+          <t>3560(5)</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="7" t="n"/>
@@ -1171,6 +1296,11 @@
           <t>Margaret_Hall</t>
         </is>
       </c>
+      <c r="G24" s="13" t="inlineStr">
+        <is>
+          <t>1878(5)</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="7" t="n"/>
@@ -1197,6 +1327,7 @@
           <t>Wind_God_Sentinel_Tower</t>
         </is>
       </c>
+      <c r="G25" s="13" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="7" t="n"/>
@@ -1223,6 +1354,11 @@
           <t>Page_Castle</t>
         </is>
       </c>
+      <c r="G26" s="13" t="inlineStr">
+        <is>
+          <t>1944(5)</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n"/>
@@ -1249,6 +1385,11 @@
           <t>Stormy_Coast</t>
         </is>
       </c>
+      <c r="G27" s="13" t="inlineStr">
+        <is>
+          <t>3830(10)</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n"/>
@@ -1275,6 +1416,11 @@
           <t>Lion_Tooth_Coast</t>
         </is>
       </c>
+      <c r="G28" s="13" t="inlineStr">
+        <is>
+          <t>3379(5)</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="7" t="n"/>
@@ -1301,6 +1447,11 @@
           <t>Ranke_Town</t>
         </is>
       </c>
+      <c r="G29" s="13" t="inlineStr">
+        <is>
+          <t>2628(5)</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="n"/>
@@ -1327,6 +1478,11 @@
           <t>Galesong_Hill</t>
         </is>
       </c>
+      <c r="G30" s="13" t="inlineStr">
+        <is>
+          <t>2649(15)</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="n"/>
@@ -1353,6 +1509,11 @@
           <t>Cape_Oath</t>
         </is>
       </c>
+      <c r="G31" s="13" t="inlineStr">
+        <is>
+          <t>4684(15)</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="7" t="n"/>
@@ -1379,6 +1540,11 @@
           <t>Eagle_Gate</t>
         </is>
       </c>
+      <c r="G32" s="13" t="inlineStr">
+        <is>
+          <t>4784(15)</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="7" t="n"/>
@@ -1405,6 +1571,11 @@
           <t>Dadaupa_Gorge</t>
         </is>
       </c>
+      <c r="G33" s="13" t="inlineStr">
+        <is>
+          <t>1344(10)</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="7" t="n"/>
@@ -1431,6 +1602,11 @@
           <t>Meaty_Tribe</t>
         </is>
       </c>
+      <c r="G34" s="13" t="inlineStr">
+        <is>
+          <t>1836(5)</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="7" t="n"/>
@@ -1457,6 +1633,11 @@
           <t>Temple_of_South_Wind_Lion</t>
         </is>
       </c>
+      <c r="G35" s="13" t="inlineStr">
+        <is>
+          <t>1370(15)</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="7" t="n"/>
@@ -1483,6 +1664,11 @@
           <t>Shapeless_Thunder</t>
         </is>
       </c>
+      <c r="G36" s="13" t="inlineStr">
+        <is>
+          <t>4797(10)</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="7" t="n"/>
@@ -1509,6 +1695,11 @@
           <t>Springvale</t>
         </is>
       </c>
+      <c r="G37" s="13" t="inlineStr">
+        <is>
+          <t>4534(5)</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="7" t="n"/>
@@ -1535,6 +1726,11 @@
           <t>Katzlein_Mount</t>
         </is>
       </c>
+      <c r="G38" s="13" t="inlineStr">
+        <is>
+          <t>4558(10)</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="n"/>
@@ -1561,6 +1757,11 @@
           <t>Vanessa_Spring</t>
         </is>
       </c>
+      <c r="G39" s="13" t="inlineStr">
+        <is>
+          <t>4598(20)</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="7" t="n"/>
@@ -1587,6 +1788,11 @@
           <t>Forget_Gorge</t>
         </is>
       </c>
+      <c r="G40" s="13" t="inlineStr">
+        <is>
+          <t>4658(15)</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="7" t="n"/>
@@ -1613,6 +1819,11 @@
           <t>Skyfrost_Nail</t>
         </is>
       </c>
+      <c r="G41" s="13" t="inlineStr">
+        <is>
+          <t>4917(11)</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="7" t="n"/>
@@ -1639,6 +1850,11 @@
           <t>Findnier_Top</t>
         </is>
       </c>
+      <c r="G42" s="13" t="inlineStr">
+        <is>
+          <t>4873(15)</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="7" t="n"/>
@@ -1665,6 +1881,11 @@
           <t>Entombed_City_Ancient_Palace</t>
         </is>
       </c>
+      <c r="G43" s="13" t="inlineStr">
+        <is>
+          <t>2172(10)</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="7" t="n"/>
@@ -1691,6 +1912,11 @@
           <t>Entombed_City_Outskirts</t>
         </is>
       </c>
+      <c r="G44" s="13" t="inlineStr">
+        <is>
+          <t>2652(5)</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="7" t="n"/>
@@ -1717,6 +1943,11 @@
           <t>Snow_Covered_Path</t>
         </is>
       </c>
+      <c r="G45" s="13" t="inlineStr">
+        <is>
+          <t>4728(5)</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="7" t="n"/>
@@ -1743,6 +1974,11 @@
           <t>Frostbearing_Tree</t>
         </is>
       </c>
+      <c r="G46" s="13" t="inlineStr">
+        <is>
+          <t>4808(20)</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="n"/>
@@ -1769,6 +2005,11 @@
           <t>Starglow_Coast</t>
         </is>
       </c>
+      <c r="G47" s="13" t="inlineStr">
+        <is>
+          <t>5068(5)</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="7" t="n"/>
@@ -1795,6 +2036,11 @@
           <t>Wyrmrest_Valley</t>
         </is>
       </c>
+      <c r="G48" s="13" t="inlineStr">
+        <is>
+          <t>2500(5)</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="7" t="n"/>
@@ -1821,6 +2067,11 @@
           <t>Schelling_Bay</t>
         </is>
       </c>
+      <c r="G49" s="13" t="inlineStr">
+        <is>
+          <t>5071(5)</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="n"/>
@@ -1847,6 +2098,11 @@
           <t>Shapeless_Ice</t>
         </is>
       </c>
+      <c r="G50" s="13" t="inlineStr">
+        <is>
+          <t>4815(10)</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="7" t="n"/>
@@ -1873,6 +2129,11 @@
           <t>Dawn_of_Winery</t>
         </is>
       </c>
+      <c r="G51" s="13" t="inlineStr">
+        <is>
+          <t>4548(20)</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="7" t="n"/>
@@ -1899,6 +2160,11 @@
           <t>Remember_Valley</t>
         </is>
       </c>
+      <c r="G52" s="13" t="inlineStr">
+        <is>
+          <t>4643(15)</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="7" t="n"/>
@@ -1925,6 +2191,11 @@
           <t>Windwail_Highland</t>
         </is>
       </c>
+      <c r="G53" s="13" t="inlineStr">
+        <is>
+          <t>2055(25)</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="7" t="n"/>
@@ -1951,6 +2222,11 @@
           <t>Drunkard_Gorge</t>
         </is>
       </c>
+      <c r="G54" s="13" t="inlineStr">
+        <is>
+          <t>4510(5)</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="7" t="n"/>
@@ -1977,6 +2253,11 @@
           <t>Domain_Of_North_Wind_Wolf</t>
         </is>
       </c>
+      <c r="G55" s="13" t="inlineStr">
+        <is>
+          <t>1174(25)</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="7" t="n"/>
@@ -2003,6 +2284,11 @@
           <t>Wolvendom</t>
         </is>
       </c>
+      <c r="G56" s="13" t="inlineStr">
+        <is>
+          <t>1341(10)</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="7" t="n"/>
@@ -2029,6 +2315,11 @@
           <t>Cecilia_Garden</t>
         </is>
       </c>
+      <c r="G57" s="13" t="inlineStr">
+        <is>
+          <t>4415(15)</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="n"/>
@@ -2055,6 +2346,11 @@
           <t>Headwind_Road</t>
         </is>
       </c>
+      <c r="G58" s="13" t="inlineStr">
+        <is>
+          <t>1590(10)</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="7" t="n"/>
@@ -2081,6 +2377,11 @@
           <t>Brightcrown_Canyon</t>
         </is>
       </c>
+      <c r="G59" s="13" t="inlineStr">
+        <is>
+          <t>4225(10)</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="7" t="n"/>
@@ -2107,6 +2408,11 @@
           <t>Brightcrown_Mountains</t>
         </is>
       </c>
+      <c r="G60" s="13" t="inlineStr">
+        <is>
+          <t>4334(5)</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="7" t="n"/>
@@ -2133,6 +2439,11 @@
           <t>Stormterror_Lair_North</t>
         </is>
       </c>
+      <c r="G61" s="13" t="inlineStr">
+        <is>
+          <t>1314(25)</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="7" t="n"/>
@@ -2159,6 +2470,11 @@
           <t>West_Wind_Mountain_West</t>
         </is>
       </c>
+      <c r="G62" s="13" t="inlineStr">
+        <is>
+          <t>1540(5)</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="7" t="n"/>
@@ -2185,6 +2501,11 @@
           <t>Breeze_Canyon</t>
         </is>
       </c>
+      <c r="G63" s="13" t="inlineStr">
+        <is>
+          <t>4195(5)</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="n"/>
@@ -2211,6 +2532,11 @@
           <t>Monson_Bay</t>
         </is>
       </c>
+      <c r="G64" s="13" t="inlineStr">
+        <is>
+          <t>4071(20)</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="7" t="n"/>
@@ -2237,6 +2563,7 @@
           <t>Brightcrown_Mountain</t>
         </is>
       </c>
+      <c r="G65" s="13" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="7" t="n"/>
@@ -2263,6 +2590,11 @@
           <t>North_Rock_Gate</t>
         </is>
       </c>
+      <c r="G66" s="13" t="inlineStr">
+        <is>
+          <t>4592(5)</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="7" t="n"/>
@@ -2289,6 +2621,7 @@
           <t>Starfell_Valley</t>
         </is>
       </c>
+      <c r="G67" s="13" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="7" t="n"/>
@@ -2315,6 +2648,11 @@
           <t>Eastern_Watch_Tower</t>
         </is>
       </c>
+      <c r="G68" s="13" t="inlineStr">
+        <is>
+          <t>4744(15)</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="7" t="n"/>
@@ -2341,6 +2679,11 @@
           <t>FAV_StarFall_City</t>
         </is>
       </c>
+      <c r="G69" s="13" t="inlineStr">
+        <is>
+          <t>4336(15)</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="7" t="n"/>
@@ -2367,6 +2710,11 @@
           <t>Frosty_Land</t>
         </is>
       </c>
+      <c r="G70" s="13" t="inlineStr">
+        <is>
+          <t>4468(5)</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="7" t="n"/>
@@ -2393,6 +2741,11 @@
           <t>MOT_WindRise_City</t>
         </is>
       </c>
+      <c r="G71" s="13" t="inlineStr">
+        <is>
+          <t>4502(10)</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="7" t="n"/>
@@ -2419,6 +2772,11 @@
           <t>Eclipse_tribe</t>
         </is>
       </c>
+      <c r="G72" s="13" t="inlineStr">
+        <is>
+          <t>952(5)</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="7" t="n"/>
@@ -2445,6 +2803,11 @@
           <t>Sleepy_Tribe</t>
         </is>
       </c>
+      <c r="G73" s="13" t="inlineStr">
+        <is>
+          <t>133(5)</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="7" t="n"/>
@@ -2471,6 +2834,11 @@
           <t>Mountaineer_Base</t>
         </is>
       </c>
+      <c r="G74" s="13" t="inlineStr">
+        <is>
+          <t>2654(10)</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="7" t="n"/>
@@ -2497,6 +2865,11 @@
           <t>Dvalin_Valley</t>
         </is>
       </c>
+      <c r="G75" s="13" t="inlineStr">
+        <is>
+          <t>4322(10)</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="7" t="n"/>
@@ -2523,6 +2896,11 @@
           <t>Wailing_Road</t>
         </is>
       </c>
+      <c r="G76" s="13" t="inlineStr">
+        <is>
+          <t>4313(10)</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="7" t="n"/>
@@ -2549,6 +2927,7 @@
           <t>Stormterror_Lair_South</t>
         </is>
       </c>
+      <c r="G77" s="13" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="7" t="n"/>
@@ -2575,6 +2954,11 @@
           <t>Tower_Surburbs</t>
         </is>
       </c>
+      <c r="G78" s="13" t="inlineStr">
+        <is>
+          <t>2893(15)</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="7" t="n"/>
@@ -2601,6 +2985,11 @@
           <t>Breeze_Coast</t>
         </is>
       </c>
+      <c r="G79" s="13" t="inlineStr">
+        <is>
+          <t>4301(5)</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="7" t="n"/>
@@ -2627,6 +3016,11 @@
           <t>Breeze_Land</t>
         </is>
       </c>
+      <c r="G80" s="13" t="inlineStr">
+        <is>
+          <t>4096(15)</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="7" t="n"/>
@@ -2653,6 +3047,11 @@
           <t>Storm_Island</t>
         </is>
       </c>
+      <c r="G81" s="13" t="inlineStr">
+        <is>
+          <t>1716(10)</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="7" t="n"/>
@@ -2679,6 +3078,11 @@
           <t>Stormterror_Harbor</t>
         </is>
       </c>
+      <c r="G82" s="13" t="inlineStr">
+        <is>
+          <t>1131(20)</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="7" t="n"/>
@@ -2705,6 +3109,11 @@
           <t>Breeze_Path</t>
         </is>
       </c>
+      <c r="G83" s="13" t="inlineStr">
+        <is>
+          <t>4101(5)</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="7" t="n"/>
@@ -2731,6 +3140,7 @@
           <t>West_Wind_Mountain_East</t>
         </is>
       </c>
+      <c r="G84" s="13" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="7" t="n"/>
@@ -2757,6 +3167,11 @@
           <t>Noble_Stairway</t>
         </is>
       </c>
+      <c r="G85" s="13" t="inlineStr">
+        <is>
+          <t>1580(10)</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="7" t="n"/>
@@ -2783,6 +3198,11 @@
           <t>Brightcrown_Corridor</t>
         </is>
       </c>
+      <c r="G86" s="13" t="inlineStr">
+        <is>
+          <t>4203(5)</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="7" t="n"/>
@@ -2809,6 +3229,11 @@
           <t>FAV_Wind_Bay</t>
         </is>
       </c>
+      <c r="G87" s="13" t="inlineStr">
+        <is>
+          <t>4129(10)</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="7" t="n"/>
@@ -2835,6 +3260,11 @@
           <t>FAV_Wine_Bay</t>
         </is>
       </c>
+      <c r="G88" s="13" t="inlineStr">
+        <is>
+          <t>2605(5)</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="7" t="n"/>
@@ -2861,6 +3291,11 @@
           <t>FAV_Clean_Port</t>
         </is>
       </c>
+      <c r="G89" s="13" t="inlineStr">
+        <is>
+          <t>635(10)</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="7" t="n"/>
@@ -2887,6 +3322,11 @@
           <t>GUN_Clean_Port</t>
         </is>
       </c>
+      <c r="G90" s="13" t="inlineStr">
+        <is>
+          <t>2476(5)</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="7" t="n"/>
@@ -2913,6 +3353,11 @@
           <t>GUN_Clean_Town</t>
         </is>
       </c>
+      <c r="G91" s="13" t="inlineStr">
+        <is>
+          <t>3948(10)</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="7" t="n"/>
@@ -2939,6 +3384,11 @@
           <t>GUN_Western_Sea</t>
         </is>
       </c>
+      <c r="G92" s="13" t="inlineStr">
+        <is>
+          <t>1667(5)</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="7" t="n"/>
@@ -2965,6 +3415,11 @@
           <t>GUN_Eastern_Sea</t>
         </is>
       </c>
+      <c r="G93" s="13" t="inlineStr">
+        <is>
+          <t>3875(10)</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="7" t="n"/>
@@ -2991,6 +3446,11 @@
           <t>GUN_JINGFU_Village</t>
         </is>
       </c>
+      <c r="G94" s="13" t="inlineStr">
+        <is>
+          <t>3909(5)</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="7" t="n"/>
@@ -3017,6 +3477,11 @@
           <t>GUN_ENorthern_Sea</t>
         </is>
       </c>
+      <c r="G95" s="13" t="inlineStr">
+        <is>
+          <t>3695(10)</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="7" t="n"/>
@@ -3043,6 +3508,11 @@
           <t>GUN_Northern_Sea</t>
         </is>
       </c>
+      <c r="G96" s="13" t="inlineStr">
+        <is>
+          <t>1368(5)</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="7" t="n"/>
@@ -3069,6 +3539,11 @@
           <t>GUN_QQ_Land2</t>
         </is>
       </c>
+      <c r="G97" s="13" t="inlineStr">
+        <is>
+          <t>3399(5)</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="7" t="n"/>
@@ -3095,6 +3570,7 @@
           <t>GUN_Second_Tower</t>
         </is>
       </c>
+      <c r="G98" s="13" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="7" t="n"/>
@@ -3121,6 +3597,11 @@
           <t>GUN_Rank_Port</t>
         </is>
       </c>
+      <c r="G99" s="13" t="inlineStr">
+        <is>
+          <t>3283(9)</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="7" t="n"/>
@@ -3147,6 +3628,11 @@
           <t>Cold_Gale_Path</t>
         </is>
       </c>
+      <c r="G100" s="13" t="inlineStr">
+        <is>
+          <t>4937(5)</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="7" t="n"/>
@@ -3173,6 +3659,11 @@
           <t>Starglow_Cavern</t>
         </is>
       </c>
+      <c r="G101" s="13" t="inlineStr">
+        <is>
+          <t>4948(5)</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="7" t="n"/>
@@ -3199,6 +3690,11 @@
           <t>Prison_Land</t>
         </is>
       </c>
+      <c r="G102" s="13" t="inlineStr">
+        <is>
+          <t>1946(5)</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="7" t="n"/>
@@ -3225,6 +3721,11 @@
           <t>Entombed_City_Waterfall</t>
         </is>
       </c>
+      <c r="G103" s="13" t="inlineStr">
+        <is>
+          <t>4834(5)</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="7" t="n"/>
@@ -3251,6 +3752,7 @@
           <t>Snow_Covered_Secret_Cave</t>
         </is>
       </c>
+      <c r="G104" s="13" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="7" t="n"/>
@@ -3277,6 +3779,11 @@
           <t>GUN_Crazy_Wind2</t>
         </is>
       </c>
+      <c r="G105" s="13" t="inlineStr">
+        <is>
+          <t>172(10)</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="7" t="n"/>
@@ -3303,6 +3810,11 @@
           <t>GUN_Crazy_Wind1</t>
         </is>
       </c>
+      <c r="G106" s="13" t="inlineStr">
+        <is>
+          <t>3793(5)</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="7" t="n"/>
@@ -3329,6 +3841,11 @@
           <t>GUN_GUN_City</t>
         </is>
       </c>
+      <c r="G107" s="13" t="inlineStr">
+        <is>
+          <t>3752(10)</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="7" t="n"/>
@@ -3355,6 +3872,11 @@
           <t>GUN_Pecky_Castle5</t>
         </is>
       </c>
+      <c r="G108" s="13" t="inlineStr">
+        <is>
+          <t>1043(5)</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="7" t="n"/>
@@ -3381,6 +3903,11 @@
           <t>GUN_Lion_Town1</t>
         </is>
       </c>
+      <c r="G109" s="13" t="inlineStr">
+        <is>
+          <t>827(5)</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="7" t="n"/>
@@ -3407,6 +3934,11 @@
           <t>GUN_Princess_Town</t>
         </is>
       </c>
+      <c r="G110" s="13" t="inlineStr">
+        <is>
+          <t>3371(5)</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="7" t="n"/>
@@ -3433,6 +3965,11 @@
           <t>GUN_Pecky_Castle4</t>
         </is>
       </c>
+      <c r="G111" s="13" t="inlineStr">
+        <is>
+          <t>3302(25)</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="7" t="n"/>
@@ -3459,6 +3996,11 @@
           <t>GUN_Western_Magret</t>
         </is>
       </c>
+      <c r="G112" s="13" t="inlineStr">
+        <is>
+          <t>3522(10)</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="7" t="n"/>
@@ -3485,6 +4027,11 @@
           <t>GUN_QQ_Land3</t>
         </is>
       </c>
+      <c r="G113" s="13" t="inlineStr">
+        <is>
+          <t>2151(10)</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="7" t="n"/>
@@ -3511,6 +4058,11 @@
           <t>GUN_Lion_Town3</t>
         </is>
       </c>
+      <c r="G114" s="13" t="inlineStr">
+        <is>
+          <t>752(25)</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="7" t="n"/>
@@ -3537,6 +4089,11 @@
           <t>GUN_Pecky_Castle2</t>
         </is>
       </c>
+      <c r="G115" s="13" t="inlineStr">
+        <is>
+          <t>502(5)</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="7" t="n"/>
@@ -3563,6 +4120,11 @@
           <t>GUN_Pecky_Castle3</t>
         </is>
       </c>
+      <c r="G116" s="13" t="inlineStr">
+        <is>
+          <t>918(10)</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="7" t="n"/>
@@ -3589,6 +4151,11 @@
           <t>GUN_Forts_Town</t>
         </is>
       </c>
+      <c r="G117" s="13" t="inlineStr">
+        <is>
+          <t>3426(10)</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="7" t="n"/>
@@ -3615,6 +4182,11 @@
           <t>GUN_ESastern_Sea</t>
         </is>
       </c>
+      <c r="G118" s="13" t="inlineStr">
+        <is>
+          <t>2792(5)</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="8" t="n"/>
@@ -3641,6 +4213,11 @@
           <t>GUN_Qie_Sea</t>
         </is>
       </c>
+      <c r="G119" s="13" t="inlineStr">
+        <is>
+          <t>2325(10)</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
@@ -3669,6 +4246,11 @@
       <c r="F120" s="12" t="inlineStr">
         <is>
           <t>Liyue_Harbor</t>
+        </is>
+      </c>
+      <c r="G120" s="13" t="inlineStr">
+        <is>
+          <t>5643(50)</t>
         </is>
       </c>
     </row>
@@ -3697,6 +4279,11 @@
           <t>Yujin_Tower</t>
         </is>
       </c>
+      <c r="G121" s="13" t="inlineStr">
+        <is>
+          <t>1153(50)</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="7" t="n"/>
@@ -3723,6 +4310,11 @@
           <t>Golden_House</t>
         </is>
       </c>
+      <c r="G122" s="13" t="inlineStr">
+        <is>
+          <t>5731(30)</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="7" t="n"/>
@@ -3749,6 +4341,11 @@
           <t>Chasm</t>
         </is>
       </c>
+      <c r="G123" s="13" t="inlineStr">
+        <is>
+          <t>1803(20)</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="7" t="n"/>
@@ -3775,6 +4372,11 @@
           <t>Yuheng_Bay</t>
         </is>
       </c>
+      <c r="G124" s="13" t="inlineStr">
+        <is>
+          <t>2064(5)</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="7" t="n"/>
@@ -3801,6 +4403,11 @@
           <t>Mt._Tianheng</t>
         </is>
       </c>
+      <c r="G125" s="13" t="inlineStr">
+        <is>
+          <t>5642(10)</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="7" t="n"/>
@@ -3827,6 +4434,11 @@
           <t>Domain_of_the_Wayward_Path</t>
         </is>
       </c>
+      <c r="G126" s="13" t="inlineStr">
+        <is>
+          <t>182(5)</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="7" t="n"/>
@@ -3853,6 +4465,11 @@
           <t>Lingju_Pass</t>
         </is>
       </c>
+      <c r="G127" s="13" t="inlineStr">
+        <is>
+          <t>2303(5)</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="7" t="n"/>
@@ -3879,6 +4496,7 @@
           <t>Lumberpick_Valley</t>
         </is>
       </c>
+      <c r="G128" s="13" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="7" t="n"/>
@@ -3905,6 +4523,11 @@
           <t>Fuao_Vale</t>
         </is>
       </c>
+      <c r="G129" s="13" t="inlineStr">
+        <is>
+          <t>5472(5)</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="7" t="n"/>
@@ -3931,6 +4554,11 @@
           <t>Glaze_Peak</t>
         </is>
       </c>
+      <c r="G130" s="13" t="inlineStr">
+        <is>
+          <t>5669(5)</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="7" t="n"/>
@@ -3957,6 +4585,11 @@
           <t>Tiangong_Gorge</t>
         </is>
       </c>
+      <c r="G131" s="13" t="inlineStr">
+        <is>
+          <t>440(10)</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="7" t="n"/>
@@ -3983,6 +4616,11 @@
           <t>Cinnabar_Cliff</t>
         </is>
       </c>
+      <c r="G132" s="13" t="inlineStr">
+        <is>
+          <t>5608(10)</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="7" t="n"/>
@@ -4009,6 +4647,11 @@
           <t>Valley_in_Chasm</t>
         </is>
       </c>
+      <c r="G133" s="13" t="inlineStr">
+        <is>
+          <t>5506(5)</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="7" t="n"/>
@@ -4035,6 +4678,11 @@
           <t>Qingxu_Pool</t>
         </is>
       </c>
+      <c r="G134" s="13" t="inlineStr">
+        <is>
+          <t>5736(5)</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="7" t="n"/>
@@ -4061,6 +4709,11 @@
           <t>Black_Rock_Village</t>
         </is>
       </c>
+      <c r="G135" s="13" t="inlineStr">
+        <is>
+          <t>5797(5)</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="7" t="n"/>
@@ -4087,6 +4740,11 @@
           <t>Dunyu_Ruins</t>
         </is>
       </c>
+      <c r="G136" s="13" t="inlineStr">
+        <is>
+          <t>2889(5)</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="7" t="n"/>
@@ -4113,6 +4771,11 @@
           <t>Luhua_Pool</t>
         </is>
       </c>
+      <c r="G137" s="13" t="inlineStr">
+        <is>
+          <t>2266(10)</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="7" t="n"/>
@@ -4139,6 +4802,11 @@
           <t>Hidden_Palace_of_Guizang_Formula</t>
         </is>
       </c>
+      <c r="G138" s="13" t="inlineStr">
+        <is>
+          <t>5293(10)</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="7" t="n"/>
@@ -4165,6 +4833,11 @@
           <t>Tianqiu_Valley</t>
         </is>
       </c>
+      <c r="G139" s="13" t="inlineStr">
+        <is>
+          <t>5306(5)</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="7" t="n"/>
@@ -4191,6 +4864,11 @@
           <t>Cuijue_Slope</t>
         </is>
       </c>
+      <c r="G140" s="13" t="inlineStr">
+        <is>
+          <t>2368(5)</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="7" t="n"/>
@@ -4217,6 +4895,11 @@
           <t>Jueyun_Karst</t>
         </is>
       </c>
+      <c r="G141" s="13" t="inlineStr">
+        <is>
+          <t>566(5)</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="7" t="n"/>
@@ -4243,6 +4926,11 @@
           <t>Taishan_Mansion</t>
         </is>
       </c>
+      <c r="G142" s="13" t="inlineStr">
+        <is>
+          <t>1858(20)</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="7" t="n"/>
@@ -4269,6 +4957,11 @@
           <t>Qingyun_Peak</t>
         </is>
       </c>
+      <c r="G143" s="13" t="inlineStr">
+        <is>
+          <t>1595(20)</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="7" t="n"/>
@@ -4295,6 +4988,11 @@
           <t>Nantianmen</t>
         </is>
       </c>
+      <c r="G144" s="13" t="inlineStr">
+        <is>
+          <t>5209(20)</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="7" t="n"/>
@@ -4321,6 +5019,11 @@
           <t>Beneath_the_Dragon-Queller</t>
         </is>
       </c>
+      <c r="G145" s="13" t="inlineStr">
+        <is>
+          <t>5086(15)</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="7" t="n"/>
@@ -4347,6 +5050,11 @@
           <t>Mt._Hulao</t>
         </is>
       </c>
+      <c r="G146" s="13" t="inlineStr">
+        <is>
+          <t>2505(10)</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="7" t="n"/>
@@ -4373,6 +5081,11 @@
           <t>Huaguang_Stone_Forest</t>
         </is>
       </c>
+      <c r="G147" s="13" t="inlineStr">
+        <is>
+          <t>4934(5)</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="7" t="n"/>
@@ -4399,6 +5112,11 @@
           <t>Mt._Aocang</t>
         </is>
       </c>
+      <c r="G148" s="13" t="inlineStr">
+        <is>
+          <t>2793(10)</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="7" t="n"/>
@@ -4425,6 +5143,11 @@
           <t>Clear_Pool_and_Mountain_Cavern</t>
         </is>
       </c>
+      <c r="G149" s="13" t="inlineStr">
+        <is>
+          <t>536(5)</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="7" t="n"/>
@@ -4451,6 +5174,7 @@
           <t>Thieves_Stone_Forest</t>
         </is>
       </c>
+      <c r="G150" s="13" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" s="7" t="n"/>
@@ -4477,6 +5201,11 @@
           <t>Ningguang_Village</t>
         </is>
       </c>
+      <c r="G151" s="13" t="inlineStr">
+        <is>
+          <t>2697(5)</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="7" t="n"/>
@@ -4503,6 +5232,11 @@
           <t>Nine_Pillars_of_Peace</t>
         </is>
       </c>
+      <c r="G152" s="13" t="inlineStr">
+        <is>
+          <t>5118(5)</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="7" t="n"/>
@@ -4529,6 +5263,11 @@
           <t>Lisha</t>
         </is>
       </c>
+      <c r="G153" s="13" t="inlineStr">
+        <is>
+          <t>1487(5)</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="7" t="n"/>
@@ -4555,6 +5294,7 @@
           <t>Guyun_Stone_Forest</t>
         </is>
       </c>
+      <c r="G154" s="13" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" s="7" t="n"/>
@@ -4581,6 +5321,11 @@
           <t>Domain_of_Guyun</t>
         </is>
       </c>
+      <c r="G155" s="13" t="inlineStr">
+        <is>
+          <t>5463(20)</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="7" t="n"/>
@@ -4607,6 +5352,11 @@
           <t>Yaoguang_Shoal</t>
         </is>
       </c>
+      <c r="G156" s="13" t="inlineStr">
+        <is>
+          <t>764(5)</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="7" t="n"/>
@@ -4633,6 +5383,11 @@
           <t>Mingyun_Village</t>
         </is>
       </c>
+      <c r="G157" s="13" t="inlineStr">
+        <is>
+          <t>5017(10)</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="7" t="n"/>
@@ -4659,6 +5414,11 @@
           <t>Hidden_Palace_of_Lianshan_Formula</t>
         </is>
       </c>
+      <c r="G158" s="13" t="inlineStr">
+        <is>
+          <t>2527(5)</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="7" t="n"/>
@@ -4685,6 +5445,11 @@
           <t>Sal_Terrae</t>
         </is>
       </c>
+      <c r="G159" s="13" t="inlineStr">
+        <is>
+          <t>4811(10)</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="7" t="n"/>
@@ -4711,6 +5476,11 @@
           <t>South_Stone_Gate</t>
         </is>
       </c>
+      <c r="G160" s="13" t="inlineStr">
+        <is>
+          <t>4682(10)</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="7" t="n"/>
@@ -4737,6 +5507,11 @@
           <t>Qingce_Village</t>
         </is>
       </c>
+      <c r="G161" s="13" t="inlineStr">
+        <is>
+          <t>4614(15)</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="7" t="n"/>
@@ -4763,6 +5538,7 @@
           <t>Wuwang_Hill</t>
         </is>
       </c>
+      <c r="G162" s="13" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" s="7" t="n"/>
@@ -4789,6 +5565,11 @@
           <t>Hidden_Palace_of_Zhou_Formula</t>
         </is>
       </c>
+      <c r="G163" s="13" t="inlineStr">
+        <is>
+          <t>44(5)</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="7" t="n"/>
@@ -4815,6 +5596,11 @@
           <t>Bishui_Plain</t>
         </is>
       </c>
+      <c r="G164" s="13" t="inlineStr">
+        <is>
+          <t>1892(10)</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="7" t="n"/>
@@ -4841,6 +5627,11 @@
           <t>Dihua_Marsh</t>
         </is>
       </c>
+      <c r="G165" s="13" t="inlineStr">
+        <is>
+          <t>2694(10)</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="7" t="n"/>
@@ -4867,6 +5658,11 @@
           <t>Wangshu_Inn</t>
         </is>
       </c>
+      <c r="G166" s="13" t="inlineStr">
+        <is>
+          <t>4930(20)</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="7" t="n"/>
@@ -4893,6 +5689,11 @@
           <t>Qingce_Terrace</t>
         </is>
       </c>
+      <c r="G167" s="13" t="inlineStr">
+        <is>
+          <t>4550(5)</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="7" t="n"/>
@@ -4919,6 +5720,11 @@
           <t>Guili_Plains</t>
         </is>
       </c>
+      <c r="G168" s="13" t="inlineStr">
+        <is>
+          <t>2104(5)</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="7" t="n"/>
@@ -4945,6 +5751,11 @@
           <t>Domain_of_Forsaken_Ruins</t>
         </is>
       </c>
+      <c r="G169" s="13" t="inlineStr">
+        <is>
+          <t>444(5)</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="7" t="n"/>
@@ -4971,6 +5782,7 @@
           <t>Guili_Bay</t>
         </is>
       </c>
+      <c r="G170" s="13" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" s="7" t="n"/>
@@ -4997,6 +5809,11 @@
           <t>Guili_Remains</t>
         </is>
       </c>
+      <c r="G171" s="13" t="inlineStr">
+        <is>
+          <t>5274(10)</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="7" t="n"/>
@@ -5023,6 +5840,7 @@
           <t>Western_Ridge_Watch</t>
         </is>
       </c>
+      <c r="G172" s="13" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" s="7" t="n"/>
@@ -5049,6 +5867,11 @@
           <t>Qiongji_Field</t>
         </is>
       </c>
+      <c r="G173" s="13" t="inlineStr">
+        <is>
+          <t>5359(10)</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="7" t="n"/>
@@ -5075,6 +5898,11 @@
           <t>Qiaoying_Village</t>
         </is>
       </c>
+      <c r="G174" s="13" t="inlineStr">
+        <is>
+          <t>4369(20)</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="7" t="n"/>
@@ -5101,6 +5929,11 @@
           <t>Chenyu_Valley</t>
         </is>
       </c>
+      <c r="G175" s="13" t="inlineStr">
+        <is>
+          <t>2841(25)</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="7" t="n"/>
@@ -5127,6 +5960,11 @@
           <t>Jade_Port</t>
         </is>
       </c>
+      <c r="G176" s="13" t="inlineStr">
+        <is>
+          <t>4355(30)</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="7" t="n"/>
@@ -5153,6 +5991,11 @@
           <t>ST_LYY_01</t>
         </is>
       </c>
+      <c r="G177" s="13" t="inlineStr">
+        <is>
+          <t>984(5)</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="7" t="n"/>
@@ -5179,6 +6022,11 @@
           <t>ST_LYY_02</t>
         </is>
       </c>
+      <c r="G178" s="13" t="inlineStr">
+        <is>
+          <t>4288(5)</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="7" t="n"/>
@@ -5205,6 +6053,11 @@
           <t>ST_LYY_03</t>
         </is>
       </c>
+      <c r="G179" s="13" t="inlineStr">
+        <is>
+          <t>4479(5)</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="7" t="n"/>
@@ -5231,6 +6084,11 @@
           <t>ST_LYY_04</t>
         </is>
       </c>
+      <c r="G180" s="13" t="inlineStr">
+        <is>
+          <t>4531(15)</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="7" t="n"/>
@@ -5257,6 +6115,11 @@
           <t>ST_LYY_05</t>
         </is>
       </c>
+      <c r="G181" s="13" t="inlineStr">
+        <is>
+          <t>2381(10)</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="7" t="n"/>
@@ -5283,6 +6146,11 @@
           <t>ST_LYY_06</t>
         </is>
       </c>
+      <c r="G182" s="13" t="inlineStr">
+        <is>
+          <t>4615(10)</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="7" t="n"/>
@@ -5309,6 +6177,11 @@
           <t>ST_LYY_07</t>
         </is>
       </c>
+      <c r="G183" s="13" t="inlineStr">
+        <is>
+          <t>4597(5)</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="7" t="n"/>
@@ -5335,6 +6208,11 @@
           <t>ST_LYY_08</t>
         </is>
       </c>
+      <c r="G184" s="13" t="inlineStr">
+        <is>
+          <t>4723(5)</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="7" t="n"/>
@@ -5361,6 +6239,11 @@
           <t>ST_LYY_09</t>
         </is>
       </c>
+      <c r="G185" s="13" t="inlineStr">
+        <is>
+          <t>2220(5)</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="7" t="n"/>
@@ -5387,6 +6270,11 @@
           <t>ST_LYY_10</t>
         </is>
       </c>
+      <c r="G186" s="13" t="inlineStr">
+        <is>
+          <t>1527(5)</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="7" t="n"/>
@@ -5413,6 +6301,11 @@
           <t>ST_LYY_11</t>
         </is>
       </c>
+      <c r="G187" s="13" t="inlineStr">
+        <is>
+          <t>374(10)</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="7" t="n"/>
@@ -5439,6 +6332,11 @@
           <t>Chihu_Rock</t>
         </is>
       </c>
+      <c r="G188" s="13" t="inlineStr">
+        <is>
+          <t>5618(5)</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="7" t="n"/>
@@ -5465,6 +6363,11 @@
           <t>Black_Rock_Factory</t>
         </is>
       </c>
+      <c r="G189" s="13" t="inlineStr">
+        <is>
+          <t>6091(20)</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="7" t="n"/>
@@ -5491,6 +6394,11 @@
           <t>Left_Tianmen_Mountain</t>
         </is>
       </c>
+      <c r="G190" s="13" t="inlineStr">
+        <is>
+          <t>1876(5)</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="7" t="n"/>
@@ -5517,6 +6425,11 @@
           <t>Right_Tianmen_Mountain</t>
         </is>
       </c>
+      <c r="G191" s="13" t="inlineStr">
+        <is>
+          <t>5393(5)</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="7" t="n"/>
@@ -5543,6 +6456,11 @@
           <t>Moon_Carver_Mount</t>
         </is>
       </c>
+      <c r="G192" s="13" t="inlineStr">
+        <is>
+          <t>5497(5)</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="7" t="n"/>
@@ -5569,6 +6487,11 @@
           <t>Water_Scenery_Valley</t>
         </is>
       </c>
+      <c r="G193" s="13" t="inlineStr">
+        <is>
+          <t>5418(20)</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="7" t="n"/>
@@ -5595,6 +6518,7 @@
           <t>Sing_World_Mount</t>
         </is>
       </c>
+      <c r="G194" s="13" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" s="7" t="n"/>
@@ -5621,6 +6545,7 @@
           <t>Cloud_Retainer_Valley</t>
         </is>
       </c>
+      <c r="G195" s="13" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" s="7" t="n"/>
@@ -5647,6 +6572,7 @@
           <t>Sea_Gazer_Mount</t>
         </is>
       </c>
+      <c r="G196" s="13" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" s="7" t="n"/>
@@ -5673,6 +6599,11 @@
           <t>Jinpeng_Ruin</t>
         </is>
       </c>
+      <c r="G197" s="13" t="inlineStr">
+        <is>
+          <t>1012(5)</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="7" t="n"/>
@@ -5699,6 +6630,11 @@
           <t>Fushe_Tomb</t>
         </is>
       </c>
+      <c r="G198" s="13" t="inlineStr">
+        <is>
+          <t>5834(10)</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="7" t="n"/>
@@ -5725,6 +6661,11 @@
           <t>Minu_Ruin</t>
         </is>
       </c>
+      <c r="G199" s="13" t="inlineStr">
+        <is>
+          <t>5546(5)</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="7" t="n"/>
@@ -5751,6 +6692,11 @@
           <t>Fanan_Ruin</t>
         </is>
       </c>
+      <c r="G200" s="13" t="inlineStr">
+        <is>
+          <t>3825(20)</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="7" t="n"/>
@@ -5777,6 +6723,11 @@
           <t>Yingda_Tomb</t>
         </is>
       </c>
+      <c r="G201" s="13" t="inlineStr">
+        <is>
+          <t>5561(5)</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="7" t="n"/>
@@ -5803,6 +6754,7 @@
           <t>Huishan_Ministry</t>
         </is>
       </c>
+      <c r="G202" s="13" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" s="7" t="n"/>
@@ -5829,6 +6781,11 @@
           <t>Yinyuan_Ministry</t>
         </is>
       </c>
+      <c r="G203" s="13" t="inlineStr">
+        <is>
+          <t>2376(10)</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="7" t="n"/>
@@ -5855,6 +6812,7 @@
           <t>Shenglu_Ministry</t>
         </is>
       </c>
+      <c r="G204" s="13" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" s="7" t="n"/>
@@ -5881,6 +6839,11 @@
           <t>Wangshan_Ministry</t>
         </is>
       </c>
+      <c r="G205" s="13" t="inlineStr">
+        <is>
+          <t>6087(5)</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="7" t="n"/>
@@ -5907,6 +6870,7 @@
           <t>Heji_Ministry</t>
         </is>
       </c>
+      <c r="G206" s="13" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" s="7" t="n"/>
@@ -5933,6 +6897,11 @@
           <t>Morax_Town</t>
         </is>
       </c>
+      <c r="G207" s="13" t="inlineStr">
+        <is>
+          <t>2828(5)</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="7" t="n"/>
@@ -5959,6 +6928,7 @@
           <t>Ningguang_Town</t>
         </is>
       </c>
+      <c r="G208" s="13" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" s="7" t="n"/>
@@ -5985,6 +6955,7 @@
           <t>Ganyu_Town</t>
         </is>
       </c>
+      <c r="G209" s="13" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" s="7" t="n"/>
@@ -6011,6 +6982,11 @@
           <t>Keqing_Town</t>
         </is>
       </c>
+      <c r="G210" s="13" t="inlineStr">
+        <is>
+          <t>5377(10)</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" s="7" t="n"/>
@@ -6037,6 +7013,11 @@
           <t>Shenhe_Town</t>
         </is>
       </c>
+      <c r="G211" s="13" t="inlineStr">
+        <is>
+          <t>5343(5)</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" s="7" t="n"/>
@@ -6063,6 +7044,7 @@
           <t>Hutao_Town</t>
         </is>
       </c>
+      <c r="G212" s="13" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" s="7" t="n"/>
@@ -6089,6 +7071,11 @@
           <t>Xiao_Town</t>
         </is>
       </c>
+      <c r="G213" s="13" t="inlineStr">
+        <is>
+          <t>5221(5)</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="7" t="n"/>
@@ -6115,6 +7102,11 @@
           <t>Yunjin_Town</t>
         </is>
       </c>
+      <c r="G214" s="13" t="inlineStr">
+        <is>
+          <t>1622(5)</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" s="7" t="n"/>
@@ -6141,6 +7133,7 @@
           <t>Guoba_Town</t>
         </is>
       </c>
+      <c r="G215" s="13" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" s="7" t="n"/>
@@ -6167,6 +7160,7 @@
           <t>Yanfei_Town</t>
         </is>
       </c>
+      <c r="G216" s="13" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" s="7" t="n"/>
@@ -6193,6 +7187,11 @@
           <t>Xingqiu_Town</t>
         </is>
       </c>
+      <c r="G217" s="13" t="inlineStr">
+        <is>
+          <t>5008(10)</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" s="7" t="n"/>
@@ -6219,6 +7218,7 @@
           <t>Xiangling_Town</t>
         </is>
       </c>
+      <c r="G218" s="13" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" s="7" t="n"/>
@@ -6245,6 +7245,11 @@
           <t>Beidou_Town</t>
         </is>
       </c>
+      <c r="G219" s="13" t="inlineStr">
+        <is>
+          <t>4976(5)</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" s="7" t="n"/>
@@ -6271,6 +7276,11 @@
           <t>Qiqi_Town</t>
         </is>
       </c>
+      <c r="G220" s="13" t="inlineStr">
+        <is>
+          <t>122(5)</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" s="7" t="n"/>
@@ -6297,6 +7307,7 @@
           <t>Xinyan_Town</t>
         </is>
       </c>
+      <c r="G221" s="13" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" s="7" t="n"/>
@@ -6323,6 +7334,7 @@
           <t>Baizhu_Town</t>
         </is>
       </c>
+      <c r="G222" s="13" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" s="7" t="n"/>
@@ -6349,6 +7361,11 @@
           <t>Yelan_Town</t>
         </is>
       </c>
+      <c r="G223" s="13" t="inlineStr">
+        <is>
+          <t>1662(5)</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" s="7" t="n"/>
@@ -6375,6 +7392,7 @@
           <t>Chongyun_Town</t>
         </is>
       </c>
+      <c r="G224" s="13" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" s="7" t="n"/>
@@ -6401,6 +7419,11 @@
           <t>Xianyun_Town</t>
         </is>
       </c>
+      <c r="G225" s="13" t="inlineStr">
+        <is>
+          <t>4693(5)</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" s="7" t="n"/>
@@ -6427,6 +7450,11 @@
           <t>Gaming_Town</t>
         </is>
       </c>
+      <c r="G226" s="13" t="inlineStr">
+        <is>
+          <t>1223(5)</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" s="7" t="n"/>
@@ -6453,6 +7481,11 @@
           <t>Sifang_Hall</t>
         </is>
       </c>
+      <c r="G227" s="13" t="inlineStr">
+        <is>
+          <t>4499(5)</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" s="7" t="n"/>
@@ -6479,6 +7512,7 @@
           <t>Dubhe_Town</t>
         </is>
       </c>
+      <c r="G228" s="13" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" s="7" t="n"/>
@@ -6505,6 +7539,11 @@
           <t>Merak_Town</t>
         </is>
       </c>
+      <c r="G229" s="13" t="inlineStr">
+        <is>
+          <t>2205(10)</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" s="7" t="n"/>
@@ -6531,6 +7570,7 @@
           <t>Geoland</t>
         </is>
       </c>
+      <c r="G230" s="13" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" s="7" t="n"/>
@@ -6557,6 +7597,11 @@
           <t>Phecda_Town</t>
         </is>
       </c>
+      <c r="G231" s="13" t="inlineStr">
+        <is>
+          <t>2117(10)</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" s="7" t="n"/>
@@ -6583,6 +7628,11 @@
           <t>Megrez_Town</t>
         </is>
       </c>
+      <c r="G232" s="13" t="inlineStr">
+        <is>
+          <t>4466(5)</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" s="7" t="n"/>
@@ -6609,6 +7659,7 @@
           <t>Alioth_Town</t>
         </is>
       </c>
+      <c r="G233" s="13" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" s="7" t="n"/>
@@ -6635,6 +7686,7 @@
           <t>Mizar_Town</t>
         </is>
       </c>
+      <c r="G234" s="13" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" s="7" t="n"/>
@@ -6661,6 +7713,7 @@
           <t>Alkaid_Town</t>
         </is>
       </c>
+      <c r="G235" s="13" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" s="7" t="n"/>
@@ -6687,6 +7740,7 @@
           <t>Solitude_Basalt</t>
         </is>
       </c>
+      <c r="G236" s="13" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" s="7" t="n"/>
@@ -6713,6 +7767,11 @@
           <t>Jagged_Peaks</t>
         </is>
       </c>
+      <c r="G237" s="13" t="inlineStr">
+        <is>
+          <t>4403(5)</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" s="7" t="n"/>
@@ -6739,6 +7798,7 @@
           <t>Creviced_Cliff</t>
         </is>
       </c>
+      <c r="G238" s="13" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" s="7" t="n"/>
@@ -6765,6 +7825,11 @@
           <t>Enduring_Jade</t>
         </is>
       </c>
+      <c r="G239" s="13" t="inlineStr">
+        <is>
+          <t>4692(5)</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" s="7" t="n"/>
@@ -6791,6 +7856,7 @@
           <t>Chiseled_Crag</t>
         </is>
       </c>
+      <c r="G240" s="13" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" s="7" t="n"/>
@@ -6817,6 +7883,7 @@
           <t>Hood_Town</t>
         </is>
       </c>
+      <c r="G241" s="13" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" s="7" t="n"/>
@@ -6843,6 +7910,7 @@
           <t>Zhaowu_Town</t>
         </is>
       </c>
+      <c r="G242" s="13" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" s="7" t="n"/>
@@ -6869,6 +7937,7 @@
           <t>Plume_Town</t>
         </is>
       </c>
+      <c r="G243" s="13" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" s="7" t="n"/>
@@ -6895,6 +7964,11 @@
           <t>Jintong_Town</t>
         </is>
       </c>
+      <c r="G244" s="13" t="inlineStr">
+        <is>
+          <t>1172(5)</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" s="7" t="n"/>
@@ -6921,6 +7995,11 @@
           <t>Sundial_Town</t>
         </is>
       </c>
+      <c r="G245" s="13" t="inlineStr">
+        <is>
+          <t>1055(5)</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" s="7" t="n"/>
@@ -6947,6 +8026,7 @@
           <t>Allegiance_Town</t>
         </is>
       </c>
+      <c r="G246" s="13" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" s="7" t="n"/>
@@ -6973,6 +8053,11 @@
           <t>Golden_Cup_Town</t>
         </is>
       </c>
+      <c r="G247" s="13" t="inlineStr">
+        <is>
+          <t>1940(5)</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" s="7" t="n"/>
@@ -6999,6 +8084,7 @@
           <t>Thundering_Might</t>
         </is>
       </c>
+      <c r="G248" s="13" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" s="7" t="n"/>
@@ -7025,6 +8111,11 @@
           <t>Keen_Extraction</t>
         </is>
       </c>
+      <c r="G249" s="13" t="inlineStr">
+        <is>
+          <t>5341(5)</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" s="7" t="n"/>
@@ -7051,6 +8142,7 @@
           <t>Foreseen_Reformation</t>
         </is>
       </c>
+      <c r="G250" s="13" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" s="7" t="n"/>
@@ -7077,6 +8169,7 @@
           <t>Attunement_Town</t>
         </is>
       </c>
+      <c r="G251" s="13" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" s="7" t="n"/>
@@ -7103,6 +8196,7 @@
           <t>Beckoning_Stars</t>
         </is>
       </c>
+      <c r="G252" s="13" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" s="8" t="n"/>
@@ -7129,6 +8223,7 @@
           <t>Tenacious_Star</t>
         </is>
       </c>
+      <c r="G253" s="13" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
@@ -7157,6 +8252,11 @@
       <c r="F254" s="6" t="inlineStr">
         <is>
           <t>Inazuma_City</t>
+        </is>
+      </c>
+      <c r="G254" s="13" t="inlineStr">
+        <is>
+          <t>6291(10)</t>
         </is>
       </c>
     </row>
@@ -7185,6 +8285,11 @@
           <t>Osaka_Castle</t>
         </is>
       </c>
+      <c r="G255" s="13" t="inlineStr">
+        <is>
+          <t>6386(50)</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" s="7" t="n"/>
@@ -7211,6 +8316,7 @@
           <t>Amakane_Island</t>
         </is>
       </c>
+      <c r="G256" s="13" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" s="7" t="n"/>
@@ -7237,6 +8343,7 @@
           <t>Byakko_Plain</t>
         </is>
       </c>
+      <c r="G257" s="13" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" s="7" t="n"/>
@@ -7263,6 +8370,7 @@
           <t>Chinju_Forest</t>
         </is>
       </c>
+      <c r="G258" s="13" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" s="7" t="n"/>
@@ -7289,6 +8397,7 @@
           <t>Mt._Yougou</t>
         </is>
       </c>
+      <c r="G259" s="13" t="inlineStr"/>
     </row>
     <row r="260">
       <c r="A260" s="7" t="n"/>
@@ -7315,6 +8424,11 @@
           <t>Grand_Narukami_Shrine</t>
         </is>
       </c>
+      <c r="G260" s="13" t="inlineStr">
+        <is>
+          <t>6062(40)</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" s="7" t="n"/>
@@ -7341,6 +8455,11 @@
           <t>Ritou</t>
         </is>
       </c>
+      <c r="G261" s="13" t="inlineStr">
+        <is>
+          <t>6092(10)</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" s="7" t="n"/>
@@ -7367,6 +8486,11 @@
           <t>Kanjou_Commission</t>
         </is>
       </c>
+      <c r="G262" s="13" t="inlineStr">
+        <is>
+          <t>6052(5)</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" s="7" t="n"/>
@@ -7393,6 +8517,11 @@
           <t>Konda_Village</t>
         </is>
       </c>
+      <c r="G263" s="13" t="inlineStr">
+        <is>
+          <t>905(1)</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" s="7" t="n"/>
@@ -7419,6 +8548,11 @@
           <t>Yashiro_Commission</t>
         </is>
       </c>
+      <c r="G264" s="13" t="inlineStr">
+        <is>
+          <t>6106(10)</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" s="7" t="n"/>
@@ -7445,6 +8579,11 @@
           <t>Wild_Sea</t>
         </is>
       </c>
+      <c r="G265" s="13" t="inlineStr">
+        <is>
+          <t>825(1)</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" s="7" t="n"/>
@@ -7471,6 +8610,11 @@
           <t>Violet_Palace</t>
         </is>
       </c>
+      <c r="G266" s="13" t="inlineStr">
+        <is>
+          <t>6350(1)</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" s="7" t="n"/>
@@ -7497,6 +8641,11 @@
           <t>Tatarasuna</t>
         </is>
       </c>
+      <c r="G267" s="13" t="inlineStr">
+        <is>
+          <t>6566(5)</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" s="7" t="n"/>
@@ -7523,6 +8672,11 @@
           <t>Royal_Shadow_Furnace</t>
         </is>
       </c>
+      <c r="G268" s="13" t="inlineStr">
+        <is>
+          <t>1402(20)</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" s="7" t="n"/>
@@ -7549,6 +8703,7 @@
           <t>Bonsai_Palace</t>
         </is>
       </c>
+      <c r="G269" s="13" t="inlineStr"/>
     </row>
     <row r="270">
       <c r="A270" s="7" t="n"/>
@@ -7575,6 +8730,11 @@
           <t>Kujou_Encampment</t>
         </is>
       </c>
+      <c r="G270" s="13" t="inlineStr">
+        <is>
+          <t>6342(5)</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" s="7" t="n"/>
@@ -7601,6 +8761,7 @@
           <t>Shapeless_Fire</t>
         </is>
       </c>
+      <c r="G271" s="13" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" s="7" t="n"/>
@@ -7627,6 +8788,11 @@
           <t>Kanazuka</t>
         </is>
       </c>
+      <c r="G272" s="13" t="inlineStr">
+        <is>
+          <t>6541(5)</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" s="7" t="n"/>
@@ -7653,6 +8819,7 @@
           <t>Nazuchi_Beach</t>
         </is>
       </c>
+      <c r="G273" s="13" t="inlineStr"/>
     </row>
     <row r="274">
       <c r="A274" s="7" t="n"/>
@@ -7679,6 +8846,11 @@
           <t>Musoujin_Gorge</t>
         </is>
       </c>
+      <c r="G274" s="13" t="inlineStr">
+        <is>
+          <t>6531(3)</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" s="7" t="n"/>
@@ -7705,6 +8877,11 @@
           <t>Fort_Fujitou</t>
         </is>
       </c>
+      <c r="G275" s="13" t="inlineStr">
+        <is>
+          <t>1783(3)</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" s="7" t="n"/>
@@ -7731,6 +8908,11 @@
           <t>Fort_Mumei</t>
         </is>
       </c>
+      <c r="G276" s="13" t="inlineStr">
+        <is>
+          <t>6572(1)</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" s="7" t="n"/>
@@ -7757,6 +8939,11 @@
           <t>Higi_Village</t>
         </is>
       </c>
+      <c r="G277" s="13" t="inlineStr">
+        <is>
+          <t>1564(5)</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" s="7" t="n"/>
@@ -7783,6 +8970,11 @@
           <t>Serpent's_Head</t>
         </is>
       </c>
+      <c r="G278" s="13" t="inlineStr">
+        <is>
+          <t>769(2)</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" s="7" t="n"/>
@@ -7809,6 +9001,11 @@
           <t>Serpent_Mine</t>
         </is>
       </c>
+      <c r="G279" s="13" t="inlineStr">
+        <is>
+          <t>6630(5)</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" s="7" t="n"/>
@@ -7835,6 +9032,11 @@
           <t>Cherry_Dye_of_the_Court</t>
         </is>
       </c>
+      <c r="G280" s="13" t="inlineStr">
+        <is>
+          <t>6561(15)</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" s="7" t="n"/>
@@ -7861,6 +9063,7 @@
           <t>Formation_Estate</t>
         </is>
       </c>
+      <c r="G281" s="13" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" s="7" t="n"/>
@@ -7887,6 +9090,11 @@
           <t>Asase_Shrine</t>
         </is>
       </c>
+      <c r="G282" s="13" t="inlineStr">
+        <is>
+          <t>2830(25)</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" s="7" t="n"/>
@@ -7913,6 +9121,7 @@
           <t>Amakumo_Peak</t>
         </is>
       </c>
+      <c r="G283" s="13" t="inlineStr"/>
     </row>
     <row r="284">
       <c r="A284" s="7" t="n"/>
@@ -7939,6 +9148,7 @@
           <t>Fort_Hiraumi</t>
         </is>
       </c>
+      <c r="G284" s="13" t="inlineStr"/>
     </row>
     <row r="285">
       <c r="A285" s="7" t="n"/>
@@ -7965,6 +9175,11 @@
           <t>Koseki_Village</t>
         </is>
       </c>
+      <c r="G285" s="13" t="inlineStr">
+        <is>
+          <t>1612(10)</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" s="7" t="n"/>
@@ -7991,6 +9206,11 @@
           <t>Seiraimaru</t>
         </is>
       </c>
+      <c r="G286" s="13" t="inlineStr">
+        <is>
+          <t>2390(1)</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" s="7" t="n"/>
@@ -8017,6 +9237,7 @@
           <t>Amakumo_East</t>
         </is>
       </c>
+      <c r="G287" s="13" t="inlineStr"/>
     </row>
     <row r="288">
       <c r="A288" s="7" t="n"/>
@@ -8043,6 +9264,7 @@
           <t>Amakumo_West</t>
         </is>
       </c>
+      <c r="G288" s="13" t="inlineStr"/>
     </row>
     <row r="289">
       <c r="A289" s="7" t="n"/>
@@ -8069,6 +9291,7 @@
           <t>Amakumo_South</t>
         </is>
       </c>
+      <c r="G289" s="13" t="inlineStr"/>
     </row>
     <row r="290">
       <c r="A290" s="7" t="n"/>
@@ -8095,6 +9318,7 @@
           <t>Tsurumi</t>
         </is>
       </c>
+      <c r="G290" s="13" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" s="7" t="n"/>
@@ -8121,6 +9345,11 @@
           <t>Autake_Plains</t>
         </is>
       </c>
+      <c r="G291" s="13" t="inlineStr">
+        <is>
+          <t>6741(3)</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" s="7" t="n"/>
@@ -8147,6 +9376,7 @@
           <t>Chirai_Shrine</t>
         </is>
       </c>
+      <c r="G292" s="13" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" s="7" t="n"/>
@@ -8173,6 +9403,7 @@
           <t>Moshiri_Ceremonial_Site</t>
         </is>
       </c>
+      <c r="G293" s="13" t="inlineStr"/>
     </row>
     <row r="294">
       <c r="A294" s="7" t="n"/>
@@ -8199,6 +9430,11 @@
           <t>Mt._Kanna</t>
         </is>
       </c>
+      <c r="G294" s="13" t="inlineStr">
+        <is>
+          <t>6744(5)</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" s="7" t="n"/>
@@ -8225,6 +9461,11 @@
           <t>Oina_Beach</t>
         </is>
       </c>
+      <c r="G295" s="13" t="inlineStr">
+        <is>
+          <t>1994(1)</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" s="7" t="n"/>
@@ -8251,6 +9492,11 @@
           <t>Shirikoro_Peak</t>
         </is>
       </c>
+      <c r="G296" s="13" t="inlineStr">
+        <is>
+          <t>6726(1)</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" s="7" t="n"/>
@@ -8277,6 +9523,7 @@
           <t>Wakukau_Shoal</t>
         </is>
       </c>
+      <c r="G297" s="13" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" s="7" t="n"/>
@@ -8303,6 +9550,7 @@
           <t>Golden_Wolflord</t>
         </is>
       </c>
+      <c r="G298" s="13" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" s="7" t="n"/>
@@ -8329,6 +9577,11 @@
           <t>Sangonomiya_Shrine</t>
         </is>
       </c>
+      <c r="G299" s="13" t="inlineStr">
+        <is>
+          <t>6573(50)</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" s="7" t="n"/>
@@ -8355,6 +9608,11 @@
           <t>Suigetsu_Pool</t>
         </is>
       </c>
+      <c r="G300" s="13" t="inlineStr">
+        <is>
+          <t>6471(1)</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" s="7" t="n"/>
@@ -8381,6 +9639,11 @@
           <t>Bourou_Village</t>
         </is>
       </c>
+      <c r="G301" s="13" t="inlineStr">
+        <is>
+          <t>6613(15)</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" s="7" t="n"/>
@@ -8407,6 +9670,11 @@
           <t>Mouun_Shrine</t>
         </is>
       </c>
+      <c r="G302" s="13" t="inlineStr">
+        <is>
+          <t>743(10)</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" s="7" t="n"/>
@@ -8433,6 +9701,7 @@
           <t>Goro_Barracks</t>
         </is>
       </c>
+      <c r="G303" s="13" t="inlineStr"/>
     </row>
     <row r="304">
       <c r="A304" s="7" t="n"/>
@@ -8459,6 +9728,7 @@
           <t>Pearl_Beach</t>
         </is>
       </c>
+      <c r="G304" s="13" t="inlineStr"/>
     </row>
     <row r="305">
       <c r="A305" s="7" t="n"/>
@@ -8485,6 +9755,7 @@
           <t>Moshiri_Kara</t>
         </is>
       </c>
+      <c r="G305" s="13" t="inlineStr"/>
     </row>
     <row r="306">
       <c r="A306" s="7" t="n"/>
@@ -8511,6 +9782,7 @@
           <t>Jinren_Island</t>
         </is>
       </c>
+      <c r="G306" s="13" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" s="7" t="n"/>
@@ -8537,6 +9809,7 @@
           <t>Electroland_308</t>
         </is>
       </c>
+      <c r="G307" s="13" t="inlineStr"/>
     </row>
     <row r="308">
       <c r="A308" s="7" t="n"/>
@@ -8563,6 +9836,7 @@
           <t>Electroland_309</t>
         </is>
       </c>
+      <c r="G308" s="13" t="inlineStr"/>
     </row>
     <row r="309">
       <c r="A309" s="7" t="n"/>
@@ -8589,6 +9863,7 @@
           <t>Electroland_310</t>
         </is>
       </c>
+      <c r="G309" s="13" t="inlineStr"/>
     </row>
     <row r="310">
       <c r="A310" s="7" t="n"/>
@@ -8615,6 +9890,11 @@
           <t>Electroland_311</t>
         </is>
       </c>
+      <c r="G310" s="13" t="inlineStr">
+        <is>
+          <t>6368(25)</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" s="7" t="n"/>
@@ -8641,6 +9921,7 @@
           <t>Electroland_312</t>
         </is>
       </c>
+      <c r="G311" s="13" t="inlineStr"/>
     </row>
     <row r="312">
       <c r="A312" s="7" t="n"/>
@@ -8667,6 +9948,7 @@
           <t>Electroland_313</t>
         </is>
       </c>
+      <c r="G312" s="13" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" s="7" t="n"/>
@@ -8693,6 +9975,7 @@
           <t>Electroland_314</t>
         </is>
       </c>
+      <c r="G313" s="13" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" s="7" t="n"/>
@@ -8719,6 +10002,7 @@
           <t>Electroland_315</t>
         </is>
       </c>
+      <c r="G314" s="13" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" s="7" t="n"/>
@@ -8745,6 +10029,11 @@
           <t>Electroland_316</t>
         </is>
       </c>
+      <c r="G315" s="13" t="inlineStr">
+        <is>
+          <t>1566(10)</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" s="7" t="n"/>
@@ -8771,6 +10060,7 @@
           <t>Electroland_317</t>
         </is>
       </c>
+      <c r="G316" s="13" t="inlineStr"/>
     </row>
     <row r="317">
       <c r="A317" s="7" t="n"/>
@@ -8797,6 +10087,7 @@
           <t>Electroland_318</t>
         </is>
       </c>
+      <c r="G317" s="13" t="inlineStr"/>
     </row>
     <row r="318">
       <c r="A318" s="7" t="n"/>
@@ -8823,6 +10114,7 @@
           <t>Electroland_319</t>
         </is>
       </c>
+      <c r="G318" s="13" t="inlineStr"/>
     </row>
     <row r="319">
       <c r="A319" s="7" t="n"/>
@@ -8849,6 +10141,7 @@
           <t>Electroland_320</t>
         </is>
       </c>
+      <c r="G319" s="13" t="inlineStr"/>
     </row>
     <row r="320">
       <c r="A320" s="7" t="n"/>
@@ -8875,6 +10168,7 @@
           <t>Electroland_321</t>
         </is>
       </c>
+      <c r="G320" s="13" t="inlineStr"/>
     </row>
     <row r="321">
       <c r="A321" s="7" t="n"/>
@@ -8901,6 +10195,7 @@
           <t>Electroland_322</t>
         </is>
       </c>
+      <c r="G321" s="13" t="inlineStr"/>
     </row>
     <row r="322">
       <c r="A322" s="7" t="n"/>
@@ -8927,6 +10222,7 @@
           <t>Electroland_323</t>
         </is>
       </c>
+      <c r="G322" s="13" t="inlineStr"/>
     </row>
     <row r="323">
       <c r="A323" s="7" t="n"/>
@@ -8953,6 +10249,11 @@
           <t>Electroland_324</t>
         </is>
       </c>
+      <c r="G323" s="13" t="inlineStr">
+        <is>
+          <t>6490(1)</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" s="7" t="n"/>
@@ -8979,6 +10280,11 @@
           <t>Electroland_325</t>
         </is>
       </c>
+      <c r="G324" s="13" t="inlineStr">
+        <is>
+          <t>402(1)</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" s="7" t="n"/>
@@ -9005,6 +10311,7 @@
           <t>Electroland_326</t>
         </is>
       </c>
+      <c r="G325" s="13" t="inlineStr"/>
     </row>
     <row r="326">
       <c r="A326" s="7" t="n"/>
@@ -9031,6 +10338,7 @@
           <t>Electroland_327</t>
         </is>
       </c>
+      <c r="G326" s="13" t="inlineStr"/>
     </row>
     <row r="327">
       <c r="A327" s="7" t="n"/>
@@ -9057,6 +10365,7 @@
           <t>Electroland_328</t>
         </is>
       </c>
+      <c r="G327" s="13" t="inlineStr"/>
     </row>
     <row r="328">
       <c r="A328" s="7" t="n"/>
@@ -9083,6 +10392,7 @@
           <t>Electroland_329</t>
         </is>
       </c>
+      <c r="G328" s="13" t="inlineStr"/>
     </row>
     <row r="329">
       <c r="A329" s="7" t="n"/>
@@ -9109,6 +10419,7 @@
           <t>Electroland_330</t>
         </is>
       </c>
+      <c r="G329" s="13" t="inlineStr"/>
     </row>
     <row r="330">
       <c r="A330" s="7" t="n"/>
@@ -9135,6 +10446,7 @@
           <t>Electroland_331</t>
         </is>
       </c>
+      <c r="G330" s="13" t="inlineStr"/>
     </row>
     <row r="331">
       <c r="A331" s="7" t="n"/>
@@ -9161,6 +10473,7 @@
           <t>Electroland_332</t>
         </is>
       </c>
+      <c r="G331" s="13" t="inlineStr"/>
     </row>
     <row r="332">
       <c r="A332" s="7" t="n"/>
@@ -9187,6 +10500,7 @@
           <t>Electroland_333</t>
         </is>
       </c>
+      <c r="G332" s="13" t="inlineStr"/>
     </row>
     <row r="333">
       <c r="A333" s="7" t="n"/>
@@ -9213,6 +10527,7 @@
           <t>Electroland_334</t>
         </is>
       </c>
+      <c r="G333" s="13" t="inlineStr"/>
     </row>
     <row r="334">
       <c r="A334" s="7" t="n"/>
@@ -9239,6 +10554,7 @@
           <t>Electroland_335</t>
         </is>
       </c>
+      <c r="G334" s="13" t="inlineStr"/>
     </row>
     <row r="335">
       <c r="A335" s="7" t="n"/>
@@ -9265,6 +10581,7 @@
           <t>Electroland_336</t>
         </is>
       </c>
+      <c r="G335" s="13" t="inlineStr"/>
     </row>
     <row r="336">
       <c r="A336" s="7" t="n"/>
@@ -9291,6 +10608,7 @@
           <t>Electroland_337</t>
         </is>
       </c>
+      <c r="G336" s="13" t="inlineStr"/>
     </row>
     <row r="337">
       <c r="A337" s="7" t="n"/>
@@ -9317,6 +10635,7 @@
           <t>Electroland_338</t>
         </is>
       </c>
+      <c r="G337" s="13" t="inlineStr"/>
     </row>
     <row r="338">
       <c r="A338" s="7" t="n"/>
@@ -9343,6 +10662,7 @@
           <t>Electroland_339</t>
         </is>
       </c>
+      <c r="G338" s="13" t="inlineStr"/>
     </row>
     <row r="339">
       <c r="A339" s="7" t="n"/>
@@ -9369,6 +10689,11 @@
           <t>Electroland_340</t>
         </is>
       </c>
+      <c r="G339" s="13" t="inlineStr">
+        <is>
+          <t>6609(1)</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" s="7" t="n"/>
@@ -9395,6 +10720,11 @@
           <t>Electroland_341</t>
         </is>
       </c>
+      <c r="G340" s="13" t="inlineStr">
+        <is>
+          <t>3825(20)</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" s="7" t="n"/>
@@ -9421,6 +10751,7 @@
           <t>Electroland_342</t>
         </is>
       </c>
+      <c r="G341" s="13" t="inlineStr"/>
     </row>
     <row r="342">
       <c r="A342" s="7" t="n"/>
@@ -9447,6 +10778,11 @@
           <t>Electroland_343</t>
         </is>
       </c>
+      <c r="G342" s="13" t="inlineStr">
+        <is>
+          <t>6571(10)</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" s="7" t="n"/>
@@ -9473,6 +10809,7 @@
           <t>Electroland_344</t>
         </is>
       </c>
+      <c r="G343" s="13" t="inlineStr"/>
     </row>
     <row r="344">
       <c r="A344" s="7" t="n"/>
@@ -9499,6 +10836,11 @@
           <t>Electroland_345</t>
         </is>
       </c>
+      <c r="G344" s="13" t="inlineStr">
+        <is>
+          <t>6282(5)</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" s="8" t="n"/>
@@ -9525,6 +10867,7 @@
           <t>Electroland_346</t>
         </is>
       </c>
+      <c r="G345" s="13" t="inlineStr"/>
     </row>
     <row r="346">
       <c r="A346" s="2" t="inlineStr">
@@ -9553,6 +10896,11 @@
       <c r="F346" s="12" t="inlineStr">
         <is>
           <t>Sumeru_City</t>
+        </is>
+      </c>
+      <c r="G346" s="13" t="inlineStr">
+        <is>
+          <t>2682(40)</t>
         </is>
       </c>
     </row>
@@ -9581,6 +10929,11 @@
           <t>Shahr_Sumeru</t>
         </is>
       </c>
+      <c r="G347" s="13" t="inlineStr">
+        <is>
+          <t>5514(20)</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" s="7" t="n"/>
@@ -9607,6 +10960,11 @@
           <t>Grand_Bazaar</t>
         </is>
       </c>
+      <c r="G348" s="13" t="inlineStr">
+        <is>
+          <t>154(20)</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" s="7" t="n"/>
@@ -9633,6 +10991,11 @@
           <t>Chinvat_Ravine</t>
         </is>
       </c>
+      <c r="G349" s="13" t="inlineStr">
+        <is>
+          <t>5611(10)</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" s="7" t="n"/>
@@ -9659,6 +11022,11 @@
           <t>Gandharva_Ville</t>
         </is>
       </c>
+      <c r="G350" s="13" t="inlineStr">
+        <is>
+          <t>5702(15)</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" s="7" t="n"/>
@@ -9685,6 +11053,11 @@
           <t>Gandha_Hill</t>
         </is>
       </c>
+      <c r="G351" s="13" t="inlineStr">
+        <is>
+          <t>1557(10)</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" s="7" t="n"/>
@@ -9711,6 +11084,11 @@
           <t>Eastern_Yazadaha_Pool</t>
         </is>
       </c>
+      <c r="G352" s="13" t="inlineStr">
+        <is>
+          <t>5639(10)</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" s="7" t="n"/>
@@ -9737,6 +11115,11 @@
           <t>Western_Yazadaha_Pool</t>
         </is>
       </c>
+      <c r="G353" s="13" t="inlineStr">
+        <is>
+          <t>1410(10)</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" s="7" t="n"/>
@@ -9763,6 +11146,11 @@
           <t>Glass_Altar_with_Seven_Leaves</t>
         </is>
       </c>
+      <c r="G354" s="13" t="inlineStr">
+        <is>
+          <t>1674(10)</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" s="7" t="n"/>
@@ -9789,6 +11177,11 @@
           <t>Avidya_Forest</t>
         </is>
       </c>
+      <c r="G355" s="13" t="inlineStr">
+        <is>
+          <t>1187(10)</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" s="7" t="n"/>
@@ -9815,6 +11208,11 @@
           <t>Mawtiyima_Forest</t>
         </is>
       </c>
+      <c r="G356" s="13" t="inlineStr">
+        <is>
+          <t>5229(5)</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" s="7" t="n"/>
@@ -9841,6 +11239,11 @@
           <t>The_shade_of_Umbrella</t>
         </is>
       </c>
+      <c r="G357" s="13" t="inlineStr">
+        <is>
+          <t>5148(10)</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" s="7" t="n"/>
@@ -9867,6 +11270,11 @@
           <t>Margin_Sleep_Tower</t>
         </is>
       </c>
+      <c r="G358" s="13" t="inlineStr">
+        <is>
+          <t>5481(10)</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" s="7" t="n"/>
@@ -9893,6 +11301,11 @@
           <t>Lokapala_Jungle</t>
         </is>
       </c>
+      <c r="G359" s="13" t="inlineStr">
+        <is>
+          <t>657(15)</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" s="7" t="n"/>
@@ -9919,6 +11332,11 @@
           <t>Chatrakam_Cave</t>
         </is>
       </c>
+      <c r="G360" s="13" t="inlineStr">
+        <is>
+          <t>1729(15)</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" s="7" t="n"/>
@@ -9945,6 +11363,11 @@
           <t>Unconscious_Tower</t>
         </is>
       </c>
+      <c r="G361" s="13" t="inlineStr">
+        <is>
+          <t>5375(5)</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" s="7" t="n"/>
@@ -9971,6 +11394,11 @@
           <t>The_Palace_of_Alcazarzaray</t>
         </is>
       </c>
+      <c r="G362" s="13" t="inlineStr">
+        <is>
+          <t>5261(10)</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" s="7" t="n"/>
@@ -9997,6 +11425,11 @@
           <t>Eastern_Vimara_Village</t>
         </is>
       </c>
+      <c r="G363" s="13" t="inlineStr">
+        <is>
+          <t>5820(20)</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" s="7" t="n"/>
@@ -10023,6 +11456,11 @@
           <t>Western_Vimara_Village</t>
         </is>
       </c>
+      <c r="G364" s="13" t="inlineStr">
+        <is>
+          <t>1735(20)</t>
+        </is>
+      </c>
     </row>
     <row r="365">
       <c r="A365" s="7" t="n"/>
@@ -10049,6 +11487,11 @@
           <t>Northern_Devantaka_Mountain</t>
         </is>
       </c>
+      <c r="G365" s="13" t="inlineStr">
+        <is>
+          <t>5845(5)</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" s="7" t="n"/>
@@ -10075,6 +11518,11 @@
           <t>Eastern_Devantaka_Mountain</t>
         </is>
       </c>
+      <c r="G366" s="13" t="inlineStr">
+        <is>
+          <t>5920(5)</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" s="7" t="n"/>
@@ -10101,6 +11549,11 @@
           <t>Southern_Devantaka_Mountain</t>
         </is>
       </c>
+      <c r="G367" s="13" t="inlineStr">
+        <is>
+          <t>5940(5)</t>
+        </is>
+      </c>
     </row>
     <row r="368">
       <c r="A368" s="7" t="n"/>
@@ -10127,6 +11580,11 @@
           <t>Ancient_Colossi_Devantaka</t>
         </is>
       </c>
+      <c r="G368" s="13" t="inlineStr">
+        <is>
+          <t>2186(5)</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" s="7" t="n"/>
@@ -10153,6 +11611,11 @@
           <t>Western_Devantaka_Mountain</t>
         </is>
       </c>
+      <c r="G369" s="13" t="inlineStr">
+        <is>
+          <t>5860(5)</t>
+        </is>
+      </c>
     </row>
     <row r="370">
       <c r="A370" s="7" t="n"/>
@@ -10179,6 +11642,11 @@
           <t>Patrolling_Forest_Site</t>
         </is>
       </c>
+      <c r="G370" s="13" t="inlineStr">
+        <is>
+          <t>5778(10)</t>
+        </is>
+      </c>
     </row>
     <row r="371">
       <c r="A371" s="7" t="n"/>
@@ -10205,6 +11673,11 @@
           <t>Western_Port_Ormos</t>
         </is>
       </c>
+      <c r="G371" s="13" t="inlineStr">
+        <is>
+          <t>6171(20)</t>
+        </is>
+      </c>
     </row>
     <row r="372">
       <c r="A372" s="7" t="n"/>
@@ -10231,6 +11704,11 @@
           <t>Eastern_Port_Ormos</t>
         </is>
       </c>
+      <c r="G372" s="13" t="inlineStr">
+        <is>
+          <t>2874(20)</t>
+        </is>
+      </c>
     </row>
     <row r="373">
       <c r="A373" s="7" t="n"/>
@@ -10257,6 +11735,11 @@
           <t>Ardravi_Valley</t>
         </is>
       </c>
+      <c r="G373" s="13" t="inlineStr">
+        <is>
+          <t>5961(5)</t>
+        </is>
+      </c>
     </row>
     <row r="374">
       <c r="A374" s="7" t="n"/>
@@ -10283,6 +11766,11 @@
           <t>The_Gloom_of_the_Valley</t>
         </is>
       </c>
+      <c r="G374" s="13" t="inlineStr">
+        <is>
+          <t>5966(5)</t>
+        </is>
+      </c>
     </row>
     <row r="375">
       <c r="A375" s="7" t="n"/>
@@ -10309,6 +11797,11 @@
           <t>Apam_Woods</t>
         </is>
       </c>
+      <c r="G375" s="13" t="inlineStr">
+        <is>
+          <t>6018(5)</t>
+        </is>
+      </c>
     </row>
     <row r="376">
       <c r="A376" s="7" t="n"/>
@@ -10335,6 +11828,11 @@
           <t>Pardis_Dhyai</t>
         </is>
       </c>
+      <c r="G376" s="13" t="inlineStr">
+        <is>
+          <t>5831(10)</t>
+        </is>
+      </c>
     </row>
     <row r="377">
       <c r="A377" s="7" t="n"/>
@@ -10361,6 +11859,11 @@
           <t>Roofed_Tower</t>
         </is>
       </c>
+      <c r="G377" s="13" t="inlineStr">
+        <is>
+          <t>6007(5)</t>
+        </is>
+      </c>
     </row>
     <row r="378">
       <c r="A378" s="7" t="n"/>
@@ -10387,6 +11890,11 @@
           <t>The_longitude_and_Weft_of_Rain</t>
         </is>
       </c>
+      <c r="G378" s="13" t="inlineStr">
+        <is>
+          <t>2242(5)</t>
+        </is>
+      </c>
     </row>
     <row r="379">
       <c r="A379" s="7" t="n"/>
@@ -10413,6 +11921,11 @@
           <t>Ruins_of_Dahri</t>
         </is>
       </c>
+      <c r="G379" s="13" t="inlineStr">
+        <is>
+          <t>6225(10)</t>
+        </is>
+      </c>
     </row>
     <row r="380">
       <c r="A380" s="7" t="n"/>
@@ -10439,6 +11952,11 @@
           <t>Caravan_Ribat</t>
         </is>
       </c>
+      <c r="G380" s="13" t="inlineStr">
+        <is>
+          <t>1323(20)</t>
+        </is>
+      </c>
     </row>
     <row r="381">
       <c r="A381" s="7" t="n"/>
@@ -10465,6 +11983,11 @@
           <t>Yasna_Monument</t>
         </is>
       </c>
+      <c r="G381" s="13" t="inlineStr">
+        <is>
+          <t>5844(5)</t>
+        </is>
+      </c>
     </row>
     <row r="382">
       <c r="A382" s="7" t="n"/>
@@ -10491,6 +12014,11 @@
           <t>Ashavan_Realm</t>
         </is>
       </c>
+      <c r="G382" s="13" t="inlineStr">
+        <is>
+          <t>6209(10)</t>
+        </is>
+      </c>
     </row>
     <row r="383">
       <c r="A383" s="7" t="n"/>
@@ -10517,6 +12045,11 @@
           <t>The_Mausoleum_of_King_Deshret</t>
         </is>
       </c>
+      <c r="G383" s="13" t="inlineStr">
+        <is>
+          <t>1708(20)</t>
+        </is>
+      </c>
     </row>
     <row r="384">
       <c r="A384" s="7" t="n"/>
@@ -10543,6 +12076,7 @@
           <t>The_Dune_of_Magma</t>
         </is>
       </c>
+      <c r="G384" s="13" t="inlineStr"/>
     </row>
     <row r="385">
       <c r="A385" s="7" t="n"/>
@@ -10569,6 +12103,7 @@
           <t>Mirage_Offering_Field</t>
         </is>
       </c>
+      <c r="G385" s="13" t="inlineStr"/>
     </row>
     <row r="386">
       <c r="A386" s="7" t="n"/>
@@ -10595,6 +12130,7 @@
           <t>The_Dune_of_Carouses</t>
         </is>
       </c>
+      <c r="G386" s="13" t="inlineStr"/>
     </row>
     <row r="387">
       <c r="A387" s="7" t="n"/>
@@ -10621,6 +12157,7 @@
           <t>The_Garden_of_Thousand_Columns</t>
         </is>
       </c>
+      <c r="G387" s="13" t="inlineStr"/>
     </row>
     <row r="388">
       <c r="A388" s="7" t="n"/>
@@ -10647,6 +12184,7 @@
           <t>The_Dune_of_Elusion</t>
         </is>
       </c>
+      <c r="G388" s="13" t="inlineStr"/>
     </row>
     <row r="389">
       <c r="A389" s="7" t="n"/>
@@ -10673,6 +12211,7 @@
           <t>Hypostyle_Desert</t>
         </is>
       </c>
+      <c r="G389" s="13" t="inlineStr"/>
     </row>
     <row r="390">
       <c r="A390" s="7" t="n"/>
@@ -10699,6 +12238,7 @@
           <t>Thousand_Years_Dragon_Beast</t>
         </is>
       </c>
+      <c r="G390" s="13" t="inlineStr"/>
     </row>
     <row r="391">
       <c r="A391" s="7" t="n"/>
@@ -10725,6 +12265,7 @@
           <t>Red_Sand_Trail</t>
         </is>
       </c>
+      <c r="G391" s="13" t="inlineStr"/>
     </row>
     <row r="392">
       <c r="A392" s="7" t="n"/>
@@ -10751,6 +12292,11 @@
           <t>Aaru_Village</t>
         </is>
       </c>
+      <c r="G392" s="13" t="inlineStr">
+        <is>
+          <t>114(40)</t>
+        </is>
+      </c>
     </row>
     <row r="393">
       <c r="A393" s="7" t="n"/>
@@ -10777,6 +12323,7 @@
           <t>Abdju_Pit</t>
         </is>
       </c>
+      <c r="G393" s="13" t="inlineStr"/>
     </row>
     <row r="394">
       <c r="A394" s="7" t="n"/>
@@ -10803,6 +12350,7 @@
           <t>The_Sill_of_Red_Sand</t>
         </is>
       </c>
+      <c r="G394" s="13" t="inlineStr"/>
     </row>
     <row r="395">
       <c r="A395" s="7" t="n"/>
@@ -10829,6 +12377,11 @@
           <t>Dar_al-Shifa</t>
         </is>
       </c>
+      <c r="G395" s="13" t="inlineStr">
+        <is>
+          <t>6278(20)</t>
+        </is>
+      </c>
     </row>
     <row r="396">
       <c r="A396" s="7" t="n"/>
@@ -10855,6 +12408,7 @@
           <t>Shapeless_Grass</t>
         </is>
       </c>
+      <c r="G396" s="13" t="inlineStr"/>
     </row>
     <row r="397">
       <c r="A397" s="7" t="n"/>
@@ -10881,6 +12435,7 @@
           <t>Saint_Hall</t>
         </is>
       </c>
+      <c r="G397" s="13" t="inlineStr"/>
     </row>
     <row r="398">
       <c r="A398" s="7" t="n"/>
@@ -10907,6 +12462,7 @@
           <t>Secret_Temple</t>
         </is>
       </c>
+      <c r="G398" s="13" t="inlineStr"/>
     </row>
     <row r="399">
       <c r="A399" s="7" t="n"/>
@@ -10933,6 +12489,7 @@
           <t>Sobek_Oasis</t>
         </is>
       </c>
+      <c r="G399" s="13" t="inlineStr"/>
     </row>
     <row r="400">
       <c r="A400" s="7" t="n"/>
@@ -10959,6 +12516,11 @@
           <t>Vanarana</t>
         </is>
       </c>
+      <c r="G400" s="13" t="inlineStr">
+        <is>
+          <t>2794(50)</t>
+        </is>
+      </c>
     </row>
     <row r="401">
       <c r="A401" s="7" t="n"/>
@@ -10985,6 +12547,11 @@
           <t>Fane_of_Ashvattha</t>
         </is>
       </c>
+      <c r="G401" s="13" t="inlineStr">
+        <is>
+          <t>323(20)</t>
+        </is>
+      </c>
     </row>
     <row r="402">
       <c r="A402" s="7" t="n"/>
@@ -11011,6 +12578,11 @@
           <t>Tree_of_Dreams</t>
         </is>
       </c>
+      <c r="G402" s="13" t="inlineStr">
+        <is>
+          <t>2552(30)</t>
+        </is>
+      </c>
     </row>
     <row r="403">
       <c r="A403" s="7" t="n"/>
@@ -11037,6 +12609,11 @@
           <t>Ranaro_Valley_East</t>
         </is>
       </c>
+      <c r="G403" s="13" t="inlineStr">
+        <is>
+          <t>1414(5)</t>
+        </is>
+      </c>
     </row>
     <row r="404">
       <c r="A404" s="7" t="n"/>
@@ -11063,6 +12640,11 @@
           <t>Lost_Nursery</t>
         </is>
       </c>
+      <c r="G404" s="13" t="inlineStr">
+        <is>
+          <t>5620(5)</t>
+        </is>
+      </c>
     </row>
     <row r="405">
       <c r="A405" s="7" t="n"/>
@@ -11089,6 +12671,11 @@
           <t>Old_Vanarana</t>
         </is>
       </c>
+      <c r="G405" s="13" t="inlineStr">
+        <is>
+          <t>5562(5)</t>
+        </is>
+      </c>
     </row>
     <row r="406">
       <c r="A406" s="7" t="n"/>
@@ -11115,6 +12702,11 @@
           <t>Gate_of_Dreams</t>
         </is>
       </c>
+      <c r="G406" s="13" t="inlineStr">
+        <is>
+          <t>5402(30)</t>
+        </is>
+      </c>
     </row>
     <row r="407">
       <c r="A407" s="7" t="n"/>
@@ -11141,6 +12733,11 @@
           <t>Giant_Kingfisher</t>
         </is>
       </c>
+      <c r="G407" s="13" t="inlineStr">
+        <is>
+          <t>5324(20)</t>
+        </is>
+      </c>
     </row>
     <row r="408">
       <c r="A408" s="7" t="n"/>
@@ -11167,6 +12764,11 @@
           <t>Valuka_Pass</t>
         </is>
       </c>
+      <c r="G408" s="13" t="inlineStr">
+        <is>
+          <t>5200(20)</t>
+        </is>
+      </c>
     </row>
     <row r="409">
       <c r="A409" s="7" t="n"/>
@@ -11193,6 +12795,11 @@
           <t>Apas_Cape</t>
         </is>
       </c>
+      <c r="G409" s="13" t="inlineStr">
+        <is>
+          <t>2249(5)</t>
+        </is>
+      </c>
     </row>
     <row r="410">
       <c r="A410" s="7" t="n"/>
@@ -11219,6 +12826,11 @@
           <t>Dasha_Ridge_North</t>
         </is>
       </c>
+      <c r="G410" s="13" t="inlineStr">
+        <is>
+          <t>4866(5)</t>
+        </is>
+      </c>
     </row>
     <row r="411">
       <c r="A411" s="7" t="n"/>
@@ -11245,6 +12857,11 @@
           <t>Bayda_Harbor</t>
         </is>
       </c>
+      <c r="G411" s="13" t="inlineStr">
+        <is>
+          <t>4985(20)</t>
+        </is>
+      </c>
     </row>
     <row r="412">
       <c r="A412" s="7" t="n"/>
@@ -11271,6 +12888,11 @@
           <t>Dasha_Ridge</t>
         </is>
       </c>
+      <c r="G412" s="13" t="inlineStr">
+        <is>
+          <t>5099(10)</t>
+        </is>
+      </c>
     </row>
     <row r="413">
       <c r="A413" s="7" t="n"/>
@@ -11297,6 +12919,11 @@
           <t>Ranaro_Valley</t>
         </is>
       </c>
+      <c r="G413" s="13" t="inlineStr">
+        <is>
+          <t>2174(10)</t>
+        </is>
+      </c>
     </row>
     <row r="414">
       <c r="A414" s="7" t="n"/>
@@ -11323,6 +12950,11 @@
           <t>Muhukunda_Mount</t>
         </is>
       </c>
+      <c r="G414" s="13" t="inlineStr">
+        <is>
+          <t>5295(5)</t>
+        </is>
+      </c>
     </row>
     <row r="415">
       <c r="A415" s="7" t="n"/>
@@ -11349,6 +12981,11 @@
           <t>Pna_Slope</t>
         </is>
       </c>
+      <c r="G415" s="13" t="inlineStr">
+        <is>
+          <t>2665(5)</t>
+        </is>
+      </c>
     </row>
     <row r="416">
       <c r="A416" s="7" t="n"/>
@@ -11375,6 +13012,11 @@
           <t>Samudra_Coast</t>
         </is>
       </c>
+      <c r="G416" s="13" t="inlineStr">
+        <is>
+          <t>4758(10)</t>
+        </is>
+      </c>
     </row>
     <row r="417">
       <c r="A417" s="7" t="n"/>
@@ -11401,6 +13043,7 @@
           <t>Qusayr_Al_Inkhida</t>
         </is>
       </c>
+      <c r="G417" s="13" t="inlineStr"/>
     </row>
     <row r="418">
       <c r="A418" s="7" t="n"/>
@@ -11427,6 +13070,7 @@
           <t>The_Sands_of_Al-Azif</t>
         </is>
       </c>
+      <c r="G418" s="13" t="inlineStr"/>
     </row>
     <row r="419">
       <c r="A419" s="7" t="n"/>
@@ -11453,6 +13097,7 @@
           <t>Wounded_Shin_Valley</t>
         </is>
       </c>
+      <c r="G419" s="13" t="inlineStr"/>
     </row>
     <row r="420">
       <c r="A420" s="7" t="n"/>
@@ -11479,6 +13124,7 @@
           <t>Debris_of_Panjvahe</t>
         </is>
       </c>
+      <c r="G420" s="13" t="inlineStr"/>
     </row>
     <row r="421">
       <c r="A421" s="7" t="n"/>
@@ -11505,6 +13151,7 @@
           <t>Safhe_Shatranj</t>
         </is>
       </c>
+      <c r="G421" s="13" t="inlineStr"/>
     </row>
     <row r="422">
       <c r="A422" s="7" t="n"/>
@@ -11531,6 +13178,7 @@
           <t>Wadi_Al_Majuj</t>
         </is>
       </c>
+      <c r="G422" s="13" t="inlineStr"/>
     </row>
     <row r="423">
       <c r="A423" s="7" t="n"/>
@@ -11557,6 +13205,7 @@
           <t>Asipattravana_Swamp</t>
         </is>
       </c>
+      <c r="G423" s="13" t="inlineStr"/>
     </row>
     <row r="424">
       <c r="A424" s="7" t="n"/>
@@ -11583,6 +13232,11 @@
           <t>Realm_of_Farakhkert</t>
         </is>
       </c>
+      <c r="G424" s="13" t="inlineStr">
+        <is>
+          <t>5002(15)</t>
+        </is>
+      </c>
     </row>
     <row r="425">
       <c r="A425" s="7" t="n"/>
@@ -11609,6 +13263,7 @@
           <t>Southern_Temir_Mountains</t>
         </is>
       </c>
+      <c r="G425" s="13" t="inlineStr"/>
     </row>
     <row r="426">
       <c r="A426" s="7" t="n"/>
@@ -11635,6 +13290,11 @@
           <t>Hills_of_Barsom</t>
         </is>
       </c>
+      <c r="G426" s="13" t="inlineStr">
+        <is>
+          <t>861(15)</t>
+        </is>
+      </c>
     </row>
     <row r="427">
       <c r="A427" s="7" t="n"/>
@@ -11661,6 +13321,11 @@
           <t>Vourukasha_Oasis</t>
         </is>
       </c>
+      <c r="G427" s="13" t="inlineStr">
+        <is>
+          <t>4869(20)</t>
+        </is>
+      </c>
     </row>
     <row r="428">
       <c r="A428" s="7" t="n"/>
@@ -11687,6 +13352,11 @@
           <t>Temir_Mountains</t>
         </is>
       </c>
+      <c r="G428" s="13" t="inlineStr">
+        <is>
+          <t>4967(10)</t>
+        </is>
+      </c>
     </row>
     <row r="429">
       <c r="A429" s="7" t="n"/>
@@ -11713,6 +13383,11 @@
           <t>Gate_of_Zulqarnain</t>
         </is>
       </c>
+      <c r="G429" s="13" t="inlineStr">
+        <is>
+          <t>4979(10)</t>
+        </is>
+      </c>
     </row>
     <row r="430">
       <c r="A430" s="7" t="n"/>
@@ -11739,6 +13414,7 @@
           <t>The_Colony_of_Pari</t>
         </is>
       </c>
+      <c r="G430" s="13" t="inlineStr"/>
     </row>
     <row r="431">
       <c r="A431" s="7" t="n"/>
@@ -11765,6 +13441,7 @@
           <t>Hangeh_Afrasiyab</t>
         </is>
       </c>
+      <c r="G431" s="13" t="inlineStr"/>
     </row>
     <row r="432">
       <c r="A432" s="7" t="n"/>
@@ -11791,6 +13468,11 @@
           <t>Valley_of_Dahri</t>
         </is>
       </c>
+      <c r="G432" s="13" t="inlineStr">
+        <is>
+          <t>6384(15)</t>
+        </is>
+      </c>
     </row>
     <row r="433">
       <c r="A433" s="7" t="n"/>
@@ -11817,6 +13499,7 @@
           <t>Kshahrewar_Palace</t>
         </is>
       </c>
+      <c r="G433" s="13" t="inlineStr"/>
     </row>
     <row r="434">
       <c r="A434" s="7" t="n"/>
@@ -11843,6 +13526,11 @@
           <t>The_Thirty_Corps_Camp</t>
         </is>
       </c>
+      <c r="G434" s="13" t="inlineStr">
+        <is>
+          <t>5565(10)</t>
+        </is>
+      </c>
     </row>
     <row r="435">
       <c r="A435" s="7" t="n"/>
@@ -11869,6 +13557,7 @@
           <t>Dendroland</t>
         </is>
       </c>
+      <c r="G435" s="13" t="inlineStr"/>
     </row>
     <row r="436">
       <c r="A436" s="7" t="n"/>
@@ -11895,6 +13584,7 @@
           <t>Dendroland</t>
         </is>
       </c>
+      <c r="G436" s="13" t="inlineStr"/>
     </row>
     <row r="437">
       <c r="A437" s="7" t="n"/>
@@ -11921,6 +13611,7 @@
           <t>Dendroland</t>
         </is>
       </c>
+      <c r="G437" s="13" t="inlineStr"/>
     </row>
     <row r="438">
       <c r="A438" s="7" t="n"/>
@@ -11947,6 +13638,7 @@
           <t>Dendroland</t>
         </is>
       </c>
+      <c r="G438" s="13" t="inlineStr"/>
     </row>
     <row r="439">
       <c r="A439" s="7" t="n"/>
@@ -11973,6 +13665,11 @@
           <t>Ormos_Port</t>
         </is>
       </c>
+      <c r="G439" s="13" t="inlineStr">
+        <is>
+          <t>1495(20)</t>
+        </is>
+      </c>
     </row>
     <row r="440">
       <c r="A440" s="7" t="n"/>
@@ -11999,6 +13696,7 @@
           <t>Dendroland</t>
         </is>
       </c>
+      <c r="G440" s="13" t="inlineStr"/>
     </row>
     <row r="441">
       <c r="A441" s="7" t="n"/>
@@ -12025,6 +13723,7 @@
           <t>Dendroland</t>
         </is>
       </c>
+      <c r="G441" s="13" t="inlineStr"/>
     </row>
     <row r="442">
       <c r="A442" s="7" t="n"/>
@@ -12051,6 +13750,11 @@
           <t>Ruin_Golem</t>
         </is>
       </c>
+      <c r="G442" s="13" t="inlineStr">
+        <is>
+          <t>5986(5)</t>
+        </is>
+      </c>
     </row>
     <row r="443">
       <c r="A443" s="7" t="n"/>
@@ -12077,6 +13781,11 @@
           <t>Southern_Pardis_Dhyai</t>
         </is>
       </c>
+      <c r="G443" s="13" t="inlineStr">
+        <is>
+          <t>5882(5)</t>
+        </is>
+      </c>
     </row>
     <row r="444">
       <c r="A444" s="7" t="n"/>
@@ -12103,6 +13812,11 @@
           <t>Sprout_cave</t>
         </is>
       </c>
+      <c r="G444" s="13" t="inlineStr">
+        <is>
+          <t>5972(10)</t>
+        </is>
+      </c>
     </row>
     <row r="445">
       <c r="A445" s="7" t="n"/>
@@ -12129,6 +13843,11 @@
           <t>Southern_Yazadaha_Pool</t>
         </is>
       </c>
+      <c r="G445" s="13" t="inlineStr">
+        <is>
+          <t>1726(5)</t>
+        </is>
+      </c>
     </row>
     <row r="446">
       <c r="A446" s="7" t="n"/>
@@ -12155,6 +13874,11 @@
           <t>Grove_of_Dreams</t>
         </is>
       </c>
+      <c r="G446" s="13" t="inlineStr">
+        <is>
+          <t>1672(5)</t>
+        </is>
+      </c>
     </row>
     <row r="447">
       <c r="A447" s="7" t="n"/>
@@ -12181,6 +13905,7 @@
           <t>Dendroland</t>
         </is>
       </c>
+      <c r="G447" s="13" t="inlineStr"/>
     </row>
     <row r="448">
       <c r="A448" s="7" t="n"/>
@@ -12207,6 +13932,11 @@
           <t>The_Rain_End</t>
         </is>
       </c>
+      <c r="G448" s="13" t="inlineStr">
+        <is>
+          <t>332(5)</t>
+        </is>
+      </c>
     </row>
     <row r="449">
       <c r="A449" s="7" t="n"/>
@@ -12233,6 +13963,7 @@
           <t>Dendroland</t>
         </is>
       </c>
+      <c r="G449" s="13" t="inlineStr"/>
     </row>
     <row r="450">
       <c r="A450" s="7" t="n"/>
@@ -12259,6 +13990,7 @@
           <t>Dendroland</t>
         </is>
       </c>
+      <c r="G450" s="13" t="inlineStr"/>
     </row>
     <row r="451">
       <c r="A451" s="7" t="n"/>
@@ -12285,6 +14017,7 @@
           <t>Dendroland</t>
         </is>
       </c>
+      <c r="G451" s="13" t="inlineStr"/>
     </row>
     <row r="452">
       <c r="A452" s="7" t="n"/>
@@ -12311,6 +14044,7 @@
           <t>Dendroland</t>
         </is>
       </c>
+      <c r="G452" s="13" t="inlineStr"/>
     </row>
     <row r="453">
       <c r="A453" s="7" t="n"/>
@@ -12337,6 +14071,7 @@
           <t>Dendroland</t>
         </is>
       </c>
+      <c r="G453" s="13" t="inlineStr"/>
     </row>
     <row r="454">
       <c r="A454" s="7" t="n"/>
@@ -12363,6 +14098,7 @@
           <t>Dendroland</t>
         </is>
       </c>
+      <c r="G454" s="13" t="inlineStr"/>
     </row>
     <row r="455">
       <c r="A455" s="7" t="n"/>
@@ -12389,6 +14125,11 @@
           <t>Vissudha_Field</t>
         </is>
       </c>
+      <c r="G455" s="13" t="inlineStr">
+        <is>
+          <t>372(10)</t>
+        </is>
+      </c>
     </row>
     <row r="456">
       <c r="A456" s="7" t="n"/>
@@ -12415,6 +14156,7 @@
           <t>Dendroland</t>
         </is>
       </c>
+      <c r="G456" s="13" t="inlineStr"/>
     </row>
     <row r="457">
       <c r="A457" s="7" t="n"/>
@@ -12441,6 +14183,11 @@
           <t>The_Slice_of_Childhood_dream</t>
         </is>
       </c>
+      <c r="G457" s="13" t="inlineStr">
+        <is>
+          <t>930(10)</t>
+        </is>
+      </c>
     </row>
     <row r="458">
       <c r="A458" s="7" t="n"/>
@@ -12467,6 +14214,11 @@
           <t>Amurta_Palace</t>
         </is>
       </c>
+      <c r="G458" s="13" t="inlineStr">
+        <is>
+          <t>5923(15)</t>
+        </is>
+      </c>
     </row>
     <row r="459">
       <c r="A459" s="7" t="n"/>
@@ -12493,6 +14245,7 @@
           <t>Eternal_Oasis</t>
         </is>
       </c>
+      <c r="G459" s="13" t="inlineStr"/>
     </row>
     <row r="460">
       <c r="A460" s="7" t="n"/>
@@ -12519,6 +14272,7 @@
           <t>Ancient_Colossi_Desert</t>
         </is>
       </c>
+      <c r="G460" s="13" t="inlineStr"/>
     </row>
     <row r="461">
       <c r="A461" s="7" t="n"/>
@@ -12545,6 +14299,7 @@
           <t>Dendroland</t>
         </is>
       </c>
+      <c r="G461" s="13" t="inlineStr"/>
     </row>
     <row r="462">
       <c r="A462" s="7" t="n"/>
@@ -12571,6 +14326,11 @@
           <t>Moon_Goddess_City</t>
         </is>
       </c>
+      <c r="G462" s="13" t="inlineStr">
+        <is>
+          <t>108(20)</t>
+        </is>
+      </c>
     </row>
     <row r="463">
       <c r="A463" s="7" t="n"/>
@@ -12597,6 +14357,11 @@
           <t>Land_of_Lower_Setekh</t>
         </is>
       </c>
+      <c r="G463" s="13" t="inlineStr">
+        <is>
+          <t>6343(15)</t>
+        </is>
+      </c>
     </row>
     <row r="464">
       <c r="A464" s="7" t="n"/>
@@ -12623,6 +14388,11 @@
           <t>One_Armed_Nagarjuna</t>
         </is>
       </c>
+      <c r="G464" s="13" t="inlineStr">
+        <is>
+          <t>2251(5)</t>
+        </is>
+      </c>
     </row>
     <row r="465">
       <c r="A465" s="7" t="n"/>
@@ -12649,6 +14419,7 @@
           <t>Wenut_Tunnels</t>
         </is>
       </c>
+      <c r="G465" s="13" t="inlineStr"/>
     </row>
     <row r="466">
       <c r="A466" s="7" t="n"/>
@@ -12675,6 +14446,11 @@
           <t>Sand_Embraced_Home</t>
         </is>
       </c>
+      <c r="G466" s="13" t="inlineStr">
+        <is>
+          <t>5985(5)</t>
+        </is>
+      </c>
     </row>
     <row r="467">
       <c r="A467" s="7" t="n"/>
@@ -12701,6 +14477,7 @@
           <t>Dendroland</t>
         </is>
       </c>
+      <c r="G467" s="13" t="inlineStr"/>
     </row>
     <row r="468">
       <c r="A468" s="7" t="n"/>
@@ -12727,6 +14504,7 @@
           <t>Arabalika_cave</t>
         </is>
       </c>
+      <c r="G468" s="13" t="inlineStr"/>
     </row>
     <row r="469">
       <c r="A469" s="7" t="n"/>
@@ -12753,6 +14531,11 @@
           <t>Eastern_Pardis_Dhyai</t>
         </is>
       </c>
+      <c r="G469" s="13" t="inlineStr">
+        <is>
+          <t>2234(10)</t>
+        </is>
+      </c>
     </row>
     <row r="470">
       <c r="A470" s="7" t="n"/>
@@ -12779,6 +14562,7 @@
           <t>Haravata_Palace</t>
         </is>
       </c>
+      <c r="G470" s="13" t="inlineStr"/>
     </row>
     <row r="471">
       <c r="A471" s="7" t="n"/>
@@ -12805,6 +14589,7 @@
           <t>Dendroland</t>
         </is>
       </c>
+      <c r="G471" s="13" t="inlineStr"/>
     </row>
     <row r="472">
       <c r="A472" s="7" t="n"/>
@@ -12831,6 +14616,7 @@
           <t>Dendroland</t>
         </is>
       </c>
+      <c r="G472" s="13" t="inlineStr"/>
     </row>
     <row r="473">
       <c r="A473" s="7" t="n"/>
@@ -12857,6 +14643,7 @@
           <t>Dendroland</t>
         </is>
       </c>
+      <c r="G473" s="13" t="inlineStr"/>
     </row>
     <row r="474">
       <c r="A474" s="7" t="n"/>
@@ -12883,6 +14670,7 @@
           <t>Dendroland</t>
         </is>
       </c>
+      <c r="G474" s="13" t="inlineStr"/>
     </row>
     <row r="475">
       <c r="A475" s="7" t="n"/>
@@ -12909,6 +14697,7 @@
           <t>Dendroland</t>
         </is>
       </c>
+      <c r="G475" s="13" t="inlineStr"/>
     </row>
     <row r="476">
       <c r="A476" s="7" t="n"/>
@@ -12935,6 +14724,7 @@
           <t>Land_of_Upper_Setekh</t>
         </is>
       </c>
+      <c r="G476" s="13" t="inlineStr"/>
     </row>
     <row r="477">
       <c r="A477" s="7" t="n"/>
@@ -12961,6 +14751,7 @@
           <t>Dendroland</t>
         </is>
       </c>
+      <c r="G477" s="13" t="inlineStr"/>
     </row>
     <row r="478">
       <c r="A478" s="7" t="n"/>
@@ -12987,6 +14778,7 @@
           <t>laboraty_of_Amurta</t>
         </is>
       </c>
+      <c r="G478" s="13" t="inlineStr"/>
     </row>
     <row r="479">
       <c r="A479" s="7" t="n"/>
@@ -13013,6 +14805,7 @@
           <t>Dendroland</t>
         </is>
       </c>
+      <c r="G479" s="13" t="inlineStr"/>
     </row>
     <row r="480">
       <c r="A480" s="7" t="n"/>
@@ -13039,6 +14832,11 @@
           <t>The_Orchard_of_Pairidaeza</t>
         </is>
       </c>
+      <c r="G480" s="13" t="inlineStr">
+        <is>
+          <t>5666(15)</t>
+        </is>
+      </c>
     </row>
     <row r="481">
       <c r="A481" s="7" t="n"/>
@@ -13065,6 +14863,7 @@
           <t>Dendroland</t>
         </is>
       </c>
+      <c r="G481" s="13" t="inlineStr"/>
     </row>
     <row r="482">
       <c r="A482" s="7" t="n"/>
@@ -13091,6 +14890,7 @@
           <t>Sunyata_Lake</t>
         </is>
       </c>
+      <c r="G482" s="13" t="inlineStr"/>
     </row>
     <row r="483">
       <c r="A483" s="7" t="n"/>
@@ -13117,6 +14917,11 @@
           <t>Farakhkert_Harbor</t>
         </is>
       </c>
+      <c r="G483" s="13" t="inlineStr">
+        <is>
+          <t>2799(10)</t>
+        </is>
+      </c>
     </row>
     <row r="484">
       <c r="A484" s="7" t="n"/>
@@ -13143,6 +14948,7 @@
           <t>Chemin_Oublie</t>
         </is>
       </c>
+      <c r="G484" s="13" t="inlineStr"/>
     </row>
     <row r="485">
       <c r="A485" s="7" t="n"/>
@@ -13169,6 +14975,7 @@
           <t>Gavireh_Lajavard_3</t>
         </is>
       </c>
+      <c r="G485" s="13" t="inlineStr"/>
     </row>
     <row r="486">
       <c r="A486" s="7" t="n"/>
@@ -13195,6 +15002,7 @@
           <t>Dendroland</t>
         </is>
       </c>
+      <c r="G486" s="13" t="inlineStr"/>
     </row>
     <row r="487">
       <c r="A487" s="7" t="n"/>
@@ -13221,6 +15029,7 @@
           <t>Dendroland</t>
         </is>
       </c>
+      <c r="G487" s="13" t="inlineStr"/>
     </row>
     <row r="488">
       <c r="A488" s="7" t="n"/>
@@ -13247,6 +15056,7 @@
           <t>Dendroland</t>
         </is>
       </c>
+      <c r="G488" s="13" t="inlineStr"/>
     </row>
     <row r="489">
       <c r="A489" s="7" t="n"/>
@@ -13273,6 +15083,7 @@
           <t>Dendroland</t>
         </is>
       </c>
+      <c r="G489" s="13" t="inlineStr"/>
     </row>
     <row r="490">
       <c r="A490" s="7" t="n"/>
@@ -13299,6 +15110,11 @@
           <t>Tunigi_Hollow</t>
         </is>
       </c>
+      <c r="G490" s="13" t="inlineStr">
+        <is>
+          <t>4913(15)</t>
+        </is>
+      </c>
     </row>
     <row r="491">
       <c r="A491" s="7" t="n"/>
@@ -13325,6 +15141,11 @@
           <t>Defense_Sand_Trail</t>
         </is>
       </c>
+      <c r="G491" s="13" t="inlineStr">
+        <is>
+          <t>2198(5)</t>
+        </is>
+      </c>
     </row>
     <row r="492">
       <c r="A492" s="7" t="n"/>
@@ -13351,6 +15172,7 @@
           <t>Dendroland</t>
         </is>
       </c>
+      <c r="G492" s="13" t="inlineStr"/>
     </row>
     <row r="493">
       <c r="A493" s="7" t="n"/>
@@ -13377,6 +15199,7 @@
           <t>Madinat_al_Nuhas</t>
         </is>
       </c>
+      <c r="G493" s="13" t="inlineStr"/>
     </row>
     <row r="494">
       <c r="A494" s="7" t="n"/>
@@ -13403,6 +15226,7 @@
           <t>Dendroland</t>
         </is>
       </c>
+      <c r="G494" s="13" t="inlineStr"/>
     </row>
     <row r="495">
       <c r="A495" s="7" t="n"/>
@@ -13429,6 +15253,7 @@
           <t>Dendroland</t>
         </is>
       </c>
+      <c r="G495" s="13" t="inlineStr"/>
     </row>
     <row r="496">
       <c r="A496" s="7" t="n"/>
@@ -13455,6 +15280,7 @@
           <t>Dendroland</t>
         </is>
       </c>
+      <c r="G496" s="13" t="inlineStr"/>
     </row>
     <row r="497">
       <c r="A497" s="8" t="n"/>
@@ -13481,6 +15307,7 @@
           <t>Dendroland</t>
         </is>
       </c>
+      <c r="G497" s="13" t="inlineStr"/>
     </row>
     <row r="498">
       <c r="A498" s="2" t="inlineStr">
@@ -13509,6 +15336,11 @@
       <c r="F498" s="6" t="inlineStr">
         <is>
           <t>Court_of_Fontaine</t>
+        </is>
+      </c>
+      <c r="G498" s="13" t="inlineStr">
+        <is>
+          <t>3914(10)</t>
         </is>
       </c>
     </row>
@@ -13537,6 +15369,11 @@
           <t>Palais_Mermonia</t>
         </is>
       </c>
+      <c r="G499" s="13" t="inlineStr">
+        <is>
+          <t>392(25)</t>
+        </is>
+      </c>
     </row>
     <row r="500">
       <c r="A500" s="7" t="n"/>
@@ -13563,6 +15400,11 @@
           <t>Opera_Epiclese</t>
         </is>
       </c>
+      <c r="G500" s="13" t="inlineStr">
+        <is>
+          <t>3954(20)</t>
+        </is>
+      </c>
     </row>
     <row r="501">
       <c r="A501" s="7" t="n"/>
@@ -13589,6 +15431,11 @@
           <t>Romaritime_Harbor</t>
         </is>
       </c>
+      <c r="G501" s="13" t="inlineStr">
+        <is>
+          <t>4579(25)</t>
+        </is>
+      </c>
     </row>
     <row r="502">
       <c r="A502" s="7" t="n"/>
@@ -13615,6 +15462,11 @@
           <t>Court_Region_Waterway_Hub</t>
         </is>
       </c>
+      <c r="G502" s="13" t="inlineStr">
+        <is>
+          <t>3966(10)</t>
+        </is>
+      </c>
     </row>
     <row r="503">
       <c r="A503" s="7" t="n"/>
@@ -13641,6 +15493,11 @@
           <t>Poisson</t>
         </is>
       </c>
+      <c r="G503" s="13" t="inlineStr">
+        <is>
+          <t>4141(10)</t>
+        </is>
+      </c>
     </row>
     <row r="504">
       <c r="A504" s="7" t="n"/>
@@ -13667,6 +15524,11 @@
           <t>Fountain_of_Lucine</t>
         </is>
       </c>
+      <c r="G504" s="13" t="inlineStr">
+        <is>
+          <t>3936(20)</t>
+        </is>
+      </c>
     </row>
     <row r="505">
       <c r="A505" s="7" t="n"/>
@@ -13693,6 +15555,11 @@
           <t>Marcotte_Station</t>
         </is>
       </c>
+      <c r="G505" s="13" t="inlineStr">
+        <is>
+          <t>1913(1)</t>
+        </is>
+      </c>
     </row>
     <row r="506">
       <c r="A506" s="7" t="n"/>
@@ -13719,6 +15586,11 @@
           <t>Mont_Esus_East</t>
         </is>
       </c>
+      <c r="G506" s="13" t="inlineStr">
+        <is>
+          <t>3463(5)</t>
+        </is>
+      </c>
     </row>
     <row r="507">
       <c r="A507" s="7" t="n"/>
@@ -13745,6 +15617,11 @@
           <t>Central_Laboratory_Ruins</t>
         </is>
       </c>
+      <c r="G507" s="13" t="inlineStr">
+        <is>
+          <t>3429(20)</t>
+        </is>
+      </c>
     </row>
     <row r="508">
       <c r="A508" s="7" t="n"/>
@@ -13771,6 +15648,7 @@
           <t>Loch_Urania</t>
         </is>
       </c>
+      <c r="G508" s="13" t="inlineStr"/>
     </row>
     <row r="509">
       <c r="A509" s="7" t="n"/>
@@ -13797,6 +15675,11 @@
           <t>Weeping_Willow_of_the_Lake</t>
         </is>
       </c>
+      <c r="G509" s="13" t="inlineStr">
+        <is>
+          <t>1546(20)</t>
+        </is>
+      </c>
     </row>
     <row r="510">
       <c r="A510" s="7" t="n"/>
@@ -13823,6 +15706,11 @@
           <t>Foggy_Forest_Path</t>
         </is>
       </c>
+      <c r="G510" s="13" t="inlineStr">
+        <is>
+          <t>3968(5)</t>
+        </is>
+      </c>
     </row>
     <row r="511">
       <c r="A511" s="7" t="n"/>
@@ -13849,6 +15737,11 @@
           <t>Lumidouce_Harbor</t>
         </is>
       </c>
+      <c r="G511" s="13" t="inlineStr">
+        <is>
+          <t>4011(20)</t>
+        </is>
+      </c>
     </row>
     <row r="512">
       <c r="A512" s="7" t="n"/>
@@ -13875,6 +15768,11 @@
           <t>Fort_Charybdis_Ruins</t>
         </is>
       </c>
+      <c r="G512" s="13" t="inlineStr">
+        <is>
+          <t>823(5)</t>
+        </is>
+      </c>
     </row>
     <row r="513">
       <c r="A513" s="7" t="n"/>
@@ -13901,6 +15799,11 @@
           <t>Mont_Automnequi</t>
         </is>
       </c>
+      <c r="G513" s="13" t="inlineStr">
+        <is>
+          <t>4222(5)</t>
+        </is>
+      </c>
     </row>
     <row r="514">
       <c r="A514" s="7" t="n"/>
@@ -13927,6 +15830,11 @@
           <t>West_Slopes_of_Mont_Automnequi</t>
         </is>
       </c>
+      <c r="G514" s="13" t="inlineStr">
+        <is>
+          <t>2514(5)</t>
+        </is>
+      </c>
     </row>
     <row r="515">
       <c r="A515" s="7" t="n"/>
@@ -13953,6 +15861,11 @@
           <t>East_Slopes_of_Mont_Automnequi</t>
         </is>
       </c>
+      <c r="G515" s="13" t="inlineStr">
+        <is>
+          <t>2157(15)</t>
+        </is>
+      </c>
     </row>
     <row r="516">
       <c r="A516" s="7" t="n"/>
@@ -13979,6 +15892,11 @@
           <t>Elynas</t>
         </is>
       </c>
+      <c r="G516" s="13" t="inlineStr">
+        <is>
+          <t>4127(10)</t>
+        </is>
+      </c>
     </row>
     <row r="517">
       <c r="A517" s="7" t="n"/>
@@ -14005,6 +15923,11 @@
           <t>Denouement_of_Sin</t>
         </is>
       </c>
+      <c r="G517" s="13" t="inlineStr">
+        <is>
+          <t>4492(15)</t>
+        </is>
+      </c>
     </row>
     <row r="518">
       <c r="A518" s="7" t="n"/>
@@ -14031,6 +15954,11 @@
           <t>New_Fontaine_Research_Institute</t>
         </is>
       </c>
+      <c r="G518" s="13" t="inlineStr">
+        <is>
+          <t>528(20)</t>
+        </is>
+      </c>
     </row>
     <row r="519">
       <c r="A519" s="7" t="n"/>
@@ -14057,6 +15985,7 @@
           <t>Hydroland_521</t>
         </is>
       </c>
+      <c r="G519" s="13" t="inlineStr"/>
     </row>
     <row r="520">
       <c r="A520" s="7" t="n"/>
@@ -14083,6 +16012,7 @@
           <t>Hydroland_522</t>
         </is>
       </c>
+      <c r="G520" s="13" t="inlineStr"/>
     </row>
     <row r="521">
       <c r="A521" s="7" t="n"/>
@@ -14109,6 +16039,7 @@
           <t>Hydroland_523</t>
         </is>
       </c>
+      <c r="G521" s="13" t="inlineStr"/>
     </row>
     <row r="522">
       <c r="A522" s="7" t="n"/>
@@ -14135,6 +16066,11 @@
           <t>Elynas_Southwest</t>
         </is>
       </c>
+      <c r="G522" s="13" t="inlineStr">
+        <is>
+          <t>1003(5)</t>
+        </is>
+      </c>
     </row>
     <row r="523">
       <c r="A523" s="7" t="n"/>
@@ -14161,6 +16097,7 @@
           <t>Elynas_Southeast</t>
         </is>
       </c>
+      <c r="G523" s="13" t="inlineStr"/>
     </row>
     <row r="524">
       <c r="A524" s="7" t="n"/>
@@ -14187,6 +16124,7 @@
           <t>Hydroland_526</t>
         </is>
       </c>
+      <c r="G524" s="13" t="inlineStr"/>
     </row>
     <row r="525">
       <c r="A525" s="7" t="n"/>
@@ -14213,6 +16151,11 @@
           <t>South_Slopes_of_Mont_Automnequi</t>
         </is>
       </c>
+      <c r="G525" s="13" t="inlineStr">
+        <is>
+          <t>2106(15)</t>
+        </is>
+      </c>
     </row>
     <row r="526">
       <c r="A526" s="7" t="n"/>
@@ -14239,6 +16182,11 @@
           <t>Wilderness_Caves</t>
         </is>
       </c>
+      <c r="G526" s="13" t="inlineStr">
+        <is>
+          <t>4286(5)</t>
+        </is>
+      </c>
     </row>
     <row r="527">
       <c r="A527" s="7" t="n"/>
@@ -14265,6 +16213,7 @@
           <t>North_Slopes_of_Mont_Automnequi</t>
         </is>
       </c>
+      <c r="G527" s="13" t="inlineStr"/>
     </row>
     <row r="528">
       <c r="A528" s="7" t="n"/>
@@ -14291,6 +16240,11 @@
           <t>Clementine_Line</t>
         </is>
       </c>
+      <c r="G528" s="13" t="inlineStr">
+        <is>
+          <t>4052(5)</t>
+        </is>
+      </c>
     </row>
     <row r="529">
       <c r="A529" s="7" t="n"/>
@@ -14317,6 +16271,7 @@
           <t>Hydroland_531</t>
         </is>
       </c>
+      <c r="G529" s="13" t="inlineStr"/>
     </row>
     <row r="530">
       <c r="A530" s="7" t="n"/>
@@ -14343,6 +16298,11 @@
           <t>Merusea_Village</t>
         </is>
       </c>
+      <c r="G530" s="13" t="inlineStr">
+        <is>
+          <t>4281(5)</t>
+        </is>
+      </c>
     </row>
     <row r="531">
       <c r="A531" s="7" t="n"/>
@@ -14369,6 +16329,11 @@
           <t>Fontaine_Hot_Springs</t>
         </is>
       </c>
+      <c r="G531" s="13" t="inlineStr">
+        <is>
+          <t>2342(10)</t>
+        </is>
+      </c>
     </row>
     <row r="532">
       <c r="A532" s="7" t="n"/>
@@ -14395,6 +16360,7 @@
           <t>Beryl_Mountains_South</t>
         </is>
       </c>
+      <c r="G532" s="13" t="inlineStr"/>
     </row>
     <row r="533">
       <c r="A533" s="7" t="n"/>
@@ -14421,6 +16387,7 @@
           <t>Beryl_Mountains_North</t>
         </is>
       </c>
+      <c r="G533" s="13" t="inlineStr"/>
     </row>
     <row r="534">
       <c r="A534" s="7" t="n"/>
@@ -14447,6 +16414,7 @@
           <t>Hydroland_536</t>
         </is>
       </c>
+      <c r="G534" s="13" t="inlineStr"/>
     </row>
     <row r="535">
       <c r="A535" s="7" t="n"/>
@@ -14473,6 +16441,7 @@
           <t>Hydroland_537</t>
         </is>
       </c>
+      <c r="G535" s="13" t="inlineStr"/>
     </row>
     <row r="536">
       <c r="A536" s="7" t="n"/>
@@ -14499,6 +16468,7 @@
           <t>Hydroland_538</t>
         </is>
       </c>
+      <c r="G536" s="13" t="inlineStr"/>
     </row>
     <row r="537">
       <c r="A537" s="7" t="n"/>
@@ -14525,6 +16495,7 @@
           <t>Hydroland_539</t>
         </is>
       </c>
+      <c r="G537" s="13" t="inlineStr"/>
     </row>
     <row r="538">
       <c r="A538" s="7" t="n"/>
@@ -14551,6 +16522,7 @@
           <t>Hydroland_540</t>
         </is>
       </c>
+      <c r="G538" s="13" t="inlineStr"/>
     </row>
     <row r="539">
       <c r="A539" s="7" t="n"/>
@@ -14577,6 +16549,7 @@
           <t>Hydroland_541</t>
         </is>
       </c>
+      <c r="G539" s="13" t="inlineStr"/>
     </row>
     <row r="540">
       <c r="A540" s="7" t="n"/>
@@ -14603,6 +16576,7 @@
           <t>Hydroland_542</t>
         </is>
       </c>
+      <c r="G540" s="13" t="inlineStr"/>
     </row>
     <row r="541">
       <c r="A541" s="7" t="n"/>
@@ -14629,6 +16603,7 @@
           <t>Hydroland_543</t>
         </is>
       </c>
+      <c r="G541" s="13" t="inlineStr"/>
     </row>
     <row r="542">
       <c r="A542" s="7" t="n"/>
@@ -14655,6 +16630,11 @@
           <t>Hydroland_544</t>
         </is>
       </c>
+      <c r="G542" s="13" t="inlineStr">
+        <is>
+          <t>1036(1)</t>
+        </is>
+      </c>
     </row>
     <row r="543">
       <c r="A543" s="7" t="n"/>
@@ -14681,6 +16661,7 @@
           <t>Hydroland_545</t>
         </is>
       </c>
+      <c r="G543" s="13" t="inlineStr"/>
     </row>
     <row r="544">
       <c r="A544" s="7" t="n"/>
@@ -14707,6 +16688,7 @@
           <t>Hydroland_546</t>
         </is>
       </c>
+      <c r="G544" s="13" t="inlineStr"/>
     </row>
     <row r="545">
       <c r="A545" s="7" t="n"/>
@@ -14733,6 +16715,7 @@
           <t>Hydroland_547</t>
         </is>
       </c>
+      <c r="G545" s="13" t="inlineStr"/>
     </row>
     <row r="546">
       <c r="A546" s="7" t="n"/>
@@ -14759,6 +16742,7 @@
           <t>Hydroland_548</t>
         </is>
       </c>
+      <c r="G546" s="13" t="inlineStr"/>
     </row>
     <row r="547">
       <c r="A547" s="7" t="n"/>
@@ -14785,6 +16769,11 @@
           <t>Hydroland_549</t>
         </is>
       </c>
+      <c r="G547" s="13" t="inlineStr">
+        <is>
+          <t>3263(1)</t>
+        </is>
+      </c>
     </row>
     <row r="548">
       <c r="A548" s="7" t="n"/>
@@ -14811,6 +16800,7 @@
           <t>Hydroland_550</t>
         </is>
       </c>
+      <c r="G548" s="13" t="inlineStr"/>
     </row>
     <row r="549">
       <c r="A549" s="7" t="n"/>
@@ -14837,6 +16827,7 @@
           <t>Hydroland_551</t>
         </is>
       </c>
+      <c r="G549" s="13" t="inlineStr"/>
     </row>
     <row r="550">
       <c r="A550" s="7" t="n"/>
@@ -14863,6 +16854,7 @@
           <t>Hydroland_552</t>
         </is>
       </c>
+      <c r="G550" s="13" t="inlineStr"/>
     </row>
     <row r="551">
       <c r="A551" s="7" t="n"/>
@@ -14889,6 +16881,7 @@
           <t>Hydroland_553</t>
         </is>
       </c>
+      <c r="G551" s="13" t="inlineStr"/>
     </row>
     <row r="552">
       <c r="A552" s="7" t="n"/>
@@ -14915,6 +16908,11 @@
           <t>Annapausis</t>
         </is>
       </c>
+      <c r="G552" s="13" t="inlineStr">
+        <is>
+          <t>710(10)</t>
+        </is>
+      </c>
     </row>
     <row r="553">
       <c r="A553" s="7" t="n"/>
@@ -14941,6 +16939,7 @@
           <t>Hydroland_555</t>
         </is>
       </c>
+      <c r="G553" s="13" t="inlineStr"/>
     </row>
     <row r="554">
       <c r="A554" s="7" t="n"/>
@@ -14967,6 +16966,11 @@
           <t>Hydroland_556</t>
         </is>
       </c>
+      <c r="G554" s="13" t="inlineStr">
+        <is>
+          <t>1538(25)</t>
+        </is>
+      </c>
     </row>
     <row r="555">
       <c r="A555" s="7" t="n"/>
@@ -14993,6 +16997,7 @@
           <t>Hydroland_557</t>
         </is>
       </c>
+      <c r="G555" s="13" t="inlineStr"/>
     </row>
     <row r="556">
       <c r="A556" s="7" t="n"/>
@@ -15019,6 +17024,7 @@
           <t>Hydroland_558</t>
         </is>
       </c>
+      <c r="G556" s="13" t="inlineStr"/>
     </row>
     <row r="557">
       <c r="A557" s="7" t="n"/>
@@ -15045,6 +17051,7 @@
           <t>Hydroland_559</t>
         </is>
       </c>
+      <c r="G557" s="13" t="inlineStr"/>
     </row>
     <row r="558">
       <c r="A558" s="7" t="n"/>
@@ -15071,6 +17078,11 @@
           <t>Hydroland_560</t>
         </is>
       </c>
+      <c r="G558" s="13" t="inlineStr">
+        <is>
+          <t>4346(5)</t>
+        </is>
+      </c>
     </row>
     <row r="559">
       <c r="A559" s="7" t="n"/>
@@ -15097,6 +17109,7 @@
           <t>Hydroland_562</t>
         </is>
       </c>
+      <c r="G559" s="13" t="inlineStr"/>
     </row>
     <row r="560">
       <c r="A560" s="7" t="n"/>
@@ -15123,6 +17136,7 @@
           <t>Hydroland_563</t>
         </is>
       </c>
+      <c r="G560" s="13" t="inlineStr"/>
     </row>
     <row r="561">
       <c r="A561" s="7" t="n"/>
@@ -15149,6 +17163,7 @@
           <t>Hydroland_564</t>
         </is>
       </c>
+      <c r="G561" s="13" t="inlineStr"/>
     </row>
     <row r="562">
       <c r="A562" s="7" t="n"/>
@@ -15175,6 +17190,7 @@
           <t>Hydroland_565</t>
         </is>
       </c>
+      <c r="G562" s="13" t="inlineStr"/>
     </row>
     <row r="563">
       <c r="A563" s="7" t="n"/>
@@ -15201,6 +17217,7 @@
           <t>Hydroland_566</t>
         </is>
       </c>
+      <c r="G563" s="13" t="inlineStr"/>
     </row>
     <row r="564">
       <c r="A564" s="7" t="n"/>
@@ -15227,6 +17244,11 @@
           <t>Institute_of_Clockwork_Applications</t>
         </is>
       </c>
+      <c r="G564" s="13" t="inlineStr">
+        <is>
+          <t>652(5)</t>
+        </is>
+      </c>
     </row>
     <row r="565">
       <c r="A565" s="7" t="n"/>
@@ -15253,6 +17275,7 @@
           <t>Hydroland_568</t>
         </is>
       </c>
+      <c r="G565" s="13" t="inlineStr"/>
     </row>
     <row r="566">
       <c r="A566" s="7" t="n"/>
@@ -15279,6 +17302,7 @@
           <t>Hydroland_569</t>
         </is>
       </c>
+      <c r="G566" s="13" t="inlineStr"/>
     </row>
     <row r="567">
       <c r="A567" s="7" t="n"/>
@@ -15305,6 +17329,7 @@
           <t>Hydroland_570</t>
         </is>
       </c>
+      <c r="G567" s="13" t="inlineStr"/>
     </row>
     <row r="568">
       <c r="A568" s="7" t="n"/>
@@ -15331,6 +17356,7 @@
           <t>Hydroland_571</t>
         </is>
       </c>
+      <c r="G568" s="13" t="inlineStr"/>
     </row>
     <row r="569">
       <c r="A569" s="7" t="n"/>
@@ -15357,6 +17383,11 @@
           <t>Research_Institute_of_Kinetic_Energy_Engineering</t>
         </is>
       </c>
+      <c r="G569" s="13" t="inlineStr">
+        <is>
+          <t>193(25)</t>
+        </is>
+      </c>
     </row>
     <row r="570">
       <c r="A570" s="7" t="n"/>
@@ -15383,6 +17414,7 @@
           <t>Hydroland_573</t>
         </is>
       </c>
+      <c r="G570" s="13" t="inlineStr"/>
     </row>
     <row r="571">
       <c r="A571" s="7" t="n"/>
@@ -15409,6 +17441,11 @@
           <t>Academic_Assembly_Hall</t>
         </is>
       </c>
+      <c r="G571" s="13" t="inlineStr">
+        <is>
+          <t>3580(20)</t>
+        </is>
+      </c>
     </row>
     <row r="572">
       <c r="A572" s="7" t="n"/>
@@ -15435,6 +17472,7 @@
           <t>Hydroland_575</t>
         </is>
       </c>
+      <c r="G572" s="13" t="inlineStr"/>
     </row>
     <row r="573">
       <c r="A573" s="7" t="n"/>
@@ -15461,6 +17499,11 @@
           <t>Hydroland_576</t>
         </is>
       </c>
+      <c r="G573" s="13" t="inlineStr">
+        <is>
+          <t>3566(5)</t>
+        </is>
+      </c>
     </row>
     <row r="574">
       <c r="A574" s="7" t="n"/>
@@ -15487,6 +17530,11 @@
           <t>Hydroland_577</t>
         </is>
       </c>
+      <c r="G574" s="13" t="inlineStr">
+        <is>
+          <t>3768(25)</t>
+        </is>
+      </c>
     </row>
     <row r="575">
       <c r="A575" s="7" t="n"/>
@@ -15513,6 +17561,11 @@
           <t>Dryas_Wood</t>
         </is>
       </c>
+      <c r="G575" s="13" t="inlineStr">
+        <is>
+          <t>3653(5)</t>
+        </is>
+      </c>
     </row>
     <row r="576">
       <c r="A576" s="7" t="n"/>
@@ -15539,6 +17592,7 @@
           <t>Hydroland_579</t>
         </is>
       </c>
+      <c r="G576" s="13" t="inlineStr"/>
     </row>
     <row r="577">
       <c r="A577" s="7" t="n"/>
@@ -15565,6 +17619,7 @@
           <t>Hydroland_580</t>
         </is>
       </c>
+      <c r="G577" s="13" t="inlineStr"/>
     </row>
     <row r="578">
       <c r="A578" s="7" t="n"/>
@@ -15591,6 +17646,7 @@
           <t>Hydroland_581</t>
         </is>
       </c>
+      <c r="G578" s="13" t="inlineStr"/>
     </row>
     <row r="579">
       <c r="A579" s="7" t="n"/>
@@ -15617,6 +17673,11 @@
           <t>Hydroland_582</t>
         </is>
       </c>
+      <c r="G579" s="13" t="inlineStr">
+        <is>
+          <t>1105(5)</t>
+        </is>
+      </c>
     </row>
     <row r="580">
       <c r="A580" s="7" t="n"/>
@@ -15643,6 +17704,11 @@
           <t>Erinnyes_Forest_Channel</t>
         </is>
       </c>
+      <c r="G580" s="13" t="inlineStr">
+        <is>
+          <t>2641(5)</t>
+        </is>
+      </c>
     </row>
     <row r="581">
       <c r="A581" s="7" t="n"/>
@@ -15669,6 +17735,11 @@
           <t>Hydroland_584</t>
         </is>
       </c>
+      <c r="G581" s="13" t="inlineStr">
+        <is>
+          <t>963(5)</t>
+        </is>
+      </c>
     </row>
     <row r="582">
       <c r="A582" s="7" t="n"/>
@@ -15695,6 +17766,11 @@
           <t>Hydroland_585</t>
         </is>
       </c>
+      <c r="G582" s="13" t="inlineStr">
+        <is>
+          <t>2036(5)</t>
+        </is>
+      </c>
     </row>
     <row r="583">
       <c r="A583" s="7" t="n"/>
@@ -15721,6 +17797,11 @@
           <t>Charybdis_Island</t>
         </is>
       </c>
+      <c r="G583" s="13" t="inlineStr">
+        <is>
+          <t>2226(25)</t>
+        </is>
+      </c>
     </row>
     <row r="584">
       <c r="A584" s="7" t="n"/>
@@ -15747,6 +17828,7 @@
           <t>Hydroland_587</t>
         </is>
       </c>
+      <c r="G584" s="13" t="inlineStr"/>
     </row>
     <row r="585">
       <c r="A585" s="7" t="n"/>
@@ -15773,6 +17855,11 @@
           <t>Tower_of_Ipsissimus</t>
         </is>
       </c>
+      <c r="G585" s="13" t="inlineStr">
+        <is>
+          <t>4189(20)</t>
+        </is>
+      </c>
     </row>
     <row r="586">
       <c r="A586" s="7" t="n"/>
@@ -15799,6 +17886,7 @@
           <t>Hydroland_589</t>
         </is>
       </c>
+      <c r="G586" s="13" t="inlineStr"/>
     </row>
     <row r="587">
       <c r="A587" s="7" t="n"/>
@@ -15825,6 +17913,7 @@
           <t>Hydroland_590</t>
         </is>
       </c>
+      <c r="G587" s="13" t="inlineStr"/>
     </row>
     <row r="588">
       <c r="A588" s="7" t="n"/>
@@ -15851,6 +17940,7 @@
           <t>Hydroland_591</t>
         </is>
       </c>
+      <c r="G588" s="13" t="inlineStr"/>
     </row>
     <row r="589">
       <c r="A589" s="7" t="n"/>
@@ -15877,6 +17967,7 @@
           <t>Hydroland_592</t>
         </is>
       </c>
+      <c r="G589" s="13" t="inlineStr"/>
     </row>
     <row r="590">
       <c r="A590" s="7" t="n"/>
@@ -15903,6 +17994,7 @@
           <t>Hydroland_593</t>
         </is>
       </c>
+      <c r="G590" s="13" t="inlineStr"/>
     </row>
     <row r="591">
       <c r="A591" s="7" t="n"/>
@@ -15929,6 +18021,7 @@
           <t>Hydroland_594</t>
         </is>
       </c>
+      <c r="G591" s="13" t="inlineStr"/>
     </row>
     <row r="592">
       <c r="A592" s="7" t="n"/>
@@ -15955,6 +18048,7 @@
           <t>Hydroland_595</t>
         </is>
       </c>
+      <c r="G592" s="13" t="inlineStr"/>
     </row>
     <row r="593">
       <c r="A593" s="7" t="n"/>
@@ -15981,6 +18075,7 @@
           <t>Hydroland</t>
         </is>
       </c>
+      <c r="G593" s="13" t="inlineStr"/>
     </row>
     <row r="594">
       <c r="A594" s="7" t="n"/>
@@ -16007,6 +18102,7 @@
           <t>Hydroland_597</t>
         </is>
       </c>
+      <c r="G594" s="13" t="inlineStr"/>
     </row>
     <row r="595">
       <c r="A595" s="7" t="n"/>
@@ -16033,6 +18129,7 @@
           <t>Hydroland_598</t>
         </is>
       </c>
+      <c r="G595" s="13" t="inlineStr"/>
     </row>
     <row r="596">
       <c r="A596" s="7" t="n"/>
@@ -16059,6 +18156,7 @@
           <t>Hydroland_599</t>
         </is>
       </c>
+      <c r="G596" s="13" t="inlineStr"/>
     </row>
     <row r="597">
       <c r="A597" s="7" t="n"/>
@@ -16085,6 +18183,11 @@
           <t>Hydrologic_Station_Channel</t>
         </is>
       </c>
+      <c r="G597" s="13" t="inlineStr">
+        <is>
+          <t>1561(10)</t>
+        </is>
+      </c>
     </row>
     <row r="598">
       <c r="A598" s="7" t="n"/>
@@ -16111,6 +18214,7 @@
           <t>Hydroland_601</t>
         </is>
       </c>
+      <c r="G598" s="13" t="inlineStr"/>
     </row>
     <row r="599">
       <c r="A599" s="7" t="n"/>
@@ -16137,6 +18241,7 @@
           <t>Hydroland_602</t>
         </is>
       </c>
+      <c r="G599" s="13" t="inlineStr"/>
     </row>
     <row r="600">
       <c r="A600" s="7" t="n"/>
@@ -16163,6 +18268,7 @@
           <t>Hydroland_603</t>
         </is>
       </c>
+      <c r="G600" s="13" t="inlineStr"/>
     </row>
     <row r="601">
       <c r="A601" s="7" t="n"/>
@@ -16189,6 +18295,7 @@
           <t>Hydroland_604</t>
         </is>
       </c>
+      <c r="G601" s="13" t="inlineStr"/>
     </row>
     <row r="602">
       <c r="A602" s="7" t="n"/>
@@ -16215,6 +18322,7 @@
           <t>Hydroland_605</t>
         </is>
       </c>
+      <c r="G602" s="13" t="inlineStr"/>
     </row>
     <row r="603">
       <c r="A603" s="7" t="n"/>
@@ -16241,6 +18349,11 @@
           <t>Quartier_Lyonnais</t>
         </is>
       </c>
+      <c r="G603" s="13" t="inlineStr">
+        <is>
+          <t>3856(5)</t>
+        </is>
+      </c>
     </row>
     <row r="604">
       <c r="A604" s="7" t="n"/>
@@ -16267,6 +18380,11 @@
           <t>Hydroland_607</t>
         </is>
       </c>
+      <c r="G604" s="13" t="inlineStr">
+        <is>
+          <t>4089(5)</t>
+        </is>
+      </c>
     </row>
     <row r="605">
       <c r="A605" s="7" t="n"/>
@@ -16293,6 +18411,11 @@
           <t>Elynas_Inside</t>
         </is>
       </c>
+      <c r="G605" s="13" t="inlineStr">
+        <is>
+          <t>4215(5)</t>
+        </is>
+      </c>
     </row>
     <row r="606">
       <c r="A606" s="7" t="n"/>
@@ -16319,6 +18442,7 @@
           <t>Hydroland_609</t>
         </is>
       </c>
+      <c r="G606" s="13" t="inlineStr"/>
     </row>
     <row r="607">
       <c r="A607" s="7" t="n"/>
@@ -16345,6 +18469,7 @@
           <t>Hydroland</t>
         </is>
       </c>
+      <c r="G607" s="13" t="inlineStr"/>
     </row>
     <row r="608">
       <c r="A608" s="7" t="n"/>
@@ -16371,6 +18496,11 @@
           <t>Hydroland_611</t>
         </is>
       </c>
+      <c r="G608" s="13" t="inlineStr">
+        <is>
+          <t>3816(5)</t>
+        </is>
+      </c>
     </row>
     <row r="609">
       <c r="A609" s="7" t="n"/>
@@ -16397,6 +18527,7 @@
           <t>Hydroland_612</t>
         </is>
       </c>
+      <c r="G609" s="13" t="inlineStr"/>
     </row>
     <row r="610">
       <c r="A610" s="7" t="n"/>
@@ -16423,6 +18554,7 @@
           <t>Hydroland</t>
         </is>
       </c>
+      <c r="G610" s="13" t="inlineStr"/>
     </row>
     <row r="611">
       <c r="A611" s="7" t="n"/>
@@ -16449,6 +18581,11 @@
           <t>Hydrological_Data_Central_Processing_Station</t>
         </is>
       </c>
+      <c r="G611" s="13" t="inlineStr">
+        <is>
+          <t>3310(5)</t>
+        </is>
+      </c>
     </row>
     <row r="612">
       <c r="A612" s="7" t="n"/>
@@ -16475,6 +18612,11 @@
           <t>Vasari_Passage</t>
         </is>
       </c>
+      <c r="G612" s="13" t="inlineStr">
+        <is>
+          <t>3962(5)</t>
+        </is>
+      </c>
     </row>
     <row r="613">
       <c r="A613" s="7" t="n"/>
@@ -16501,6 +18643,11 @@
           <t>Mont_Esus</t>
         </is>
       </c>
+      <c r="G613" s="13" t="inlineStr">
+        <is>
+          <t>3799(15)</t>
+        </is>
+      </c>
     </row>
     <row r="614">
       <c r="A614" s="7" t="n"/>
@@ -16527,6 +18674,7 @@
           <t>Hydroland_617</t>
         </is>
       </c>
+      <c r="G614" s="13" t="inlineStr"/>
     </row>
     <row r="615">
       <c r="A615" s="7" t="n"/>
@@ -16553,6 +18701,7 @@
           <t>Hydroland_618</t>
         </is>
       </c>
+      <c r="G615" s="13" t="inlineStr"/>
     </row>
     <row r="616">
       <c r="A616" s="7" t="n"/>
@@ -16579,6 +18728,11 @@
           <t>Hydroland_619</t>
         </is>
       </c>
+      <c r="G616" s="13" t="inlineStr">
+        <is>
+          <t>179(10)</t>
+        </is>
+      </c>
     </row>
     <row r="617">
       <c r="A617" s="7" t="n"/>
@@ -16605,6 +18759,7 @@
           <t>Hydroland_620</t>
         </is>
       </c>
+      <c r="G617" s="13" t="inlineStr"/>
     </row>
     <row r="618">
       <c r="A618" s="7" t="n"/>
@@ -16631,6 +18786,7 @@
           <t>Hydroland_621</t>
         </is>
       </c>
+      <c r="G618" s="13" t="inlineStr"/>
     </row>
     <row r="619">
       <c r="A619" s="7" t="n"/>
@@ -16657,6 +18813,7 @@
           <t>Hydroland</t>
         </is>
       </c>
+      <c r="G619" s="13" t="inlineStr"/>
     </row>
     <row r="620">
       <c r="A620" s="7" t="n"/>
@@ -16683,6 +18840,7 @@
           <t>Hydroland_623</t>
         </is>
       </c>
+      <c r="G620" s="13" t="inlineStr"/>
     </row>
     <row r="621">
       <c r="A621" s="7" t="n"/>
@@ -16709,6 +18867,11 @@
           <t>Quartier_Narbonnais</t>
         </is>
       </c>
+      <c r="G621" s="13" t="inlineStr">
+        <is>
+          <t>3910(10)</t>
+        </is>
+      </c>
     </row>
     <row r="622">
       <c r="A622" s="7" t="n"/>
@@ -16735,6 +18898,7 @@
           <t>Hydroland_625</t>
         </is>
       </c>
+      <c r="G622" s="13" t="inlineStr"/>
     </row>
     <row r="623">
       <c r="A623" s="8" t="n"/>
@@ -16761,6 +18925,7 @@
           <t>Hydroland_626</t>
         </is>
       </c>
+      <c r="G623" s="13" t="inlineStr"/>
     </row>
     <row r="624">
       <c r="A624" s="2" t="inlineStr">
@@ -16791,6 +18956,7 @@
           <t>Pyroland</t>
         </is>
       </c>
+      <c r="G624" s="13" t="inlineStr"/>
     </row>
     <row r="625">
       <c r="A625" s="7" t="n"/>
@@ -16817,6 +18983,11 @@
           <t>Tequemecam_Valley</t>
         </is>
       </c>
+      <c r="G625" s="13" t="inlineStr">
+        <is>
+          <t>149(10)</t>
+        </is>
+      </c>
     </row>
     <row r="626">
       <c r="A626" s="7" t="n"/>
@@ -16843,6 +19014,11 @@
           <t>Basin_of_Unnumbered_Flames</t>
         </is>
       </c>
+      <c r="G626" s="13" t="inlineStr">
+        <is>
+          <t>119(10)</t>
+        </is>
+      </c>
     </row>
     <row r="627">
       <c r="A627" s="7" t="n"/>
@@ -16869,6 +19045,11 @@
           <t>Sulfurous_Veins</t>
         </is>
       </c>
+      <c r="G627" s="13" t="inlineStr">
+        <is>
+          <t>212(10)</t>
+        </is>
+      </c>
     </row>
     <row r="628">
       <c r="A628" s="7" t="n"/>
@@ -16895,6 +19076,11 @@
           <t>Stadium_of_the_Sacred_Flame</t>
         </is>
       </c>
+      <c r="G628" s="13" t="inlineStr">
+        <is>
+          <t>847(100)</t>
+        </is>
+      </c>
     </row>
     <row r="629">
       <c r="A629" s="7" t="n"/>
@@ -16921,6 +19107,11 @@
           <t>Rift_in_the_Mountains</t>
         </is>
       </c>
+      <c r="G629" s="13" t="inlineStr">
+        <is>
+          <t>8(10)</t>
+        </is>
+      </c>
     </row>
     <row r="630">
       <c r="A630" s="7" t="n"/>
@@ -16947,6 +19138,11 @@
           <t>Collective_of_Plenty</t>
         </is>
       </c>
+      <c r="G630" s="13" t="inlineStr">
+        <is>
+          <t>1309(20)</t>
+        </is>
+      </c>
     </row>
     <row r="631">
       <c r="A631" s="7" t="n"/>
@@ -16973,6 +19169,11 @@
           <t>Land_of_Myriad_Megaliths</t>
         </is>
       </c>
+      <c r="G631" s="13" t="inlineStr">
+        <is>
+          <t>78(10)</t>
+        </is>
+      </c>
     </row>
     <row r="632">
       <c r="A632" s="7" t="n"/>
@@ -16999,6 +19200,11 @@
           <t>Scions_of_the_Canopy</t>
         </is>
       </c>
+      <c r="G632" s="13" t="inlineStr">
+        <is>
+          <t>501(20)</t>
+        </is>
+      </c>
     </row>
     <row r="633">
       <c r="A633" s="7" t="n"/>
@@ -17025,6 +19231,11 @@
           <t>Children_of_Echoes</t>
         </is>
       </c>
+      <c r="G633" s="13" t="inlineStr">
+        <is>
+          <t>427(20)</t>
+        </is>
+      </c>
     </row>
     <row r="634">
       <c r="A634" s="7" t="n"/>
@@ -17051,6 +19262,11 @@
           <t>Huitztli_Hill</t>
         </is>
       </c>
+      <c r="G634" s="13" t="inlineStr">
+        <is>
+          <t>11(10)</t>
+        </is>
+      </c>
     </row>
     <row r="635">
       <c r="A635" s="7" t="n"/>
@@ -17077,6 +19293,11 @@
           <t>Chuwen_Fair</t>
         </is>
       </c>
+      <c r="G635" s="13" t="inlineStr">
+        <is>
+          <t>615(10)</t>
+        </is>
+      </c>
     </row>
     <row r="636">
       <c r="A636" s="7" t="n"/>
@@ -17103,6 +19324,11 @@
           <t>Tablet_of_Tona</t>
         </is>
       </c>
+      <c r="G636" s="13" t="inlineStr">
+        <is>
+          <t>25(10)</t>
+        </is>
+      </c>
     </row>
     <row r="637">
       <c r="A637" s="7" t="n"/>
@@ -17129,6 +19355,11 @@
           <t>Speaker's_Chamber</t>
         </is>
       </c>
+      <c r="G637" s="13" t="inlineStr">
+        <is>
+          <t>521(10)</t>
+        </is>
+      </c>
     </row>
     <row r="638">
       <c r="A638" s="7" t="n"/>
@@ -17155,6 +19386,11 @@
           <t>Coatepec_Mountain</t>
         </is>
       </c>
+      <c r="G638" s="13" t="inlineStr">
+        <is>
+          <t>64(10)</t>
+        </is>
+      </c>
     </row>
     <row r="639">
       <c r="A639" s="7" t="n"/>
@@ -17181,6 +19417,11 @@
           <t>Firethief's_Secret_Isle</t>
         </is>
       </c>
+      <c r="G639" s="13" t="inlineStr">
+        <is>
+          <t>80(10)</t>
+        </is>
+      </c>
     </row>
     <row r="640">
       <c r="A640" s="7" t="n"/>
@@ -17207,6 +19448,11 @@
           <t>Night_Kingdom</t>
         </is>
       </c>
+      <c r="G640" s="13" t="inlineStr">
+        <is>
+          <t>290(10)</t>
+        </is>
+      </c>
     </row>
     <row r="641">
       <c r="A641" s="7" t="n"/>
@@ -17233,6 +19479,7 @@
           <t>Pyroland</t>
         </is>
       </c>
+      <c r="G641" s="13" t="inlineStr"/>
     </row>
     <row r="642">
       <c r="A642" s="7" t="n"/>
@@ -17259,6 +19506,7 @@
           <t>Pyroland</t>
         </is>
       </c>
+      <c r="G642" s="13" t="inlineStr"/>
     </row>
     <row r="643">
       <c r="A643" s="7" t="n"/>
@@ -17285,6 +19533,11 @@
           <t>People_of_the_Springs</t>
         </is>
       </c>
+      <c r="G643" s="13" t="inlineStr">
+        <is>
+          <t>866(20)</t>
+        </is>
+      </c>
     </row>
     <row r="644">
       <c r="A644" s="7" t="n"/>
@@ -17311,6 +19564,7 @@
           <t>Pyroland</t>
         </is>
       </c>
+      <c r="G644" s="13" t="inlineStr"/>
     </row>
     <row r="645">
       <c r="A645" s="7" t="n"/>
@@ -17337,6 +19591,7 @@
           <t>Pyroland</t>
         </is>
       </c>
+      <c r="G645" s="13" t="inlineStr"/>
     </row>
     <row r="646">
       <c r="A646" s="7" t="n"/>
@@ -17363,6 +19618,7 @@
           <t>Pyroland</t>
         </is>
       </c>
+      <c r="G646" s="13" t="inlineStr"/>
     </row>
     <row r="647">
       <c r="A647" s="7" t="n"/>
@@ -17389,6 +19645,7 @@
           <t>Pyroland</t>
         </is>
       </c>
+      <c r="G647" s="13" t="inlineStr"/>
     </row>
     <row r="648">
       <c r="A648" s="7" t="n"/>
@@ -17415,6 +19672,7 @@
           <t>Pyroland</t>
         </is>
       </c>
+      <c r="G648" s="13" t="inlineStr"/>
     </row>
     <row r="649">
       <c r="A649" s="7" t="n"/>
@@ -17441,6 +19699,11 @@
           <t>Tepeacac_Rise</t>
         </is>
       </c>
+      <c r="G649" s="13" t="inlineStr">
+        <is>
+          <t>1116(10)</t>
+        </is>
+      </c>
     </row>
     <row r="650">
       <c r="A650" s="7" t="n"/>
@@ -17467,6 +19730,11 @@
           <t>Ochkanatlan</t>
         </is>
       </c>
+      <c r="G650" s="13" t="inlineStr">
+        <is>
+          <t>1159(20)</t>
+        </is>
+      </c>
     </row>
     <row r="651">
       <c r="A651" s="7" t="n"/>
@@ -17493,6 +19761,7 @@
           <t>Pyroland</t>
         </is>
       </c>
+      <c r="G651" s="13" t="inlineStr"/>
     </row>
     <row r="652">
       <c r="A652" s="8" t="n"/>
@@ -17519,6 +19788,11 @@
           <t>Pyroland</t>
         </is>
       </c>
+      <c r="G652" s="13" t="inlineStr">
+        <is>
+          <t>23(20)</t>
+        </is>
+      </c>
     </row>
     <row r="653">
       <c r="A653" s="2" t="inlineStr">
@@ -17547,6 +19821,11 @@
       <c r="F653" s="6" t="inlineStr">
         <is>
           <t>Nasha_Town</t>
+        </is>
+      </c>
+      <c r="G653" s="13" t="inlineStr">
+        <is>
+          <t>20(40)</t>
         </is>
       </c>
     </row>
@@ -17575,6 +19854,11 @@
           <t>Welkin_Moon</t>
         </is>
       </c>
+      <c r="G654" s="13" t="inlineStr">
+        <is>
+          <t>4090(10)</t>
+        </is>
+      </c>
     </row>
     <row r="655">
       <c r="A655" s="7" t="n"/>
@@ -17601,6 +19885,11 @@
           <t>Welkin_Moon</t>
         </is>
       </c>
+      <c r="G655" s="13" t="inlineStr">
+        <is>
+          <t>11397(10)</t>
+        </is>
+      </c>
     </row>
     <row r="656">
       <c r="A656" s="7" t="n"/>
@@ -17627,6 +19916,11 @@
           <t>Barrowmoss_Barrens</t>
         </is>
       </c>
+      <c r="G656" s="13" t="inlineStr">
+        <is>
+          <t>11398(10)</t>
+        </is>
+      </c>
     </row>
     <row r="657">
       <c r="A657" s="7" t="n"/>
@@ -17653,6 +19947,11 @@
           <t>Design_Bureau</t>
         </is>
       </c>
+      <c r="G657" s="13" t="inlineStr">
+        <is>
+          <t>1056(20)</t>
+        </is>
+      </c>
     </row>
     <row r="658">
       <c r="A658" s="7" t="n"/>
@@ -17679,6 +19978,11 @@
           <t>Welkin_Moon</t>
         </is>
       </c>
+      <c r="G658" s="13" t="inlineStr">
+        <is>
+          <t>164(10)</t>
+        </is>
+      </c>
     </row>
     <row r="659">
       <c r="A659" s="7" t="n"/>
@@ -17705,6 +20009,11 @@
           <t>Welkin_Moon</t>
         </is>
       </c>
+      <c r="G659" s="13" t="inlineStr">
+        <is>
+          <t>55(10)</t>
+        </is>
+      </c>
     </row>
     <row r="660">
       <c r="A660" s="7" t="n"/>
@@ -17731,6 +20040,11 @@
           <t>Welkin_Moon</t>
         </is>
       </c>
+      <c r="G660" s="13" t="inlineStr">
+        <is>
+          <t>42(10)</t>
+        </is>
+      </c>
     </row>
     <row r="661">
       <c r="A661" s="7" t="n"/>
@@ -17757,6 +20071,11 @@
           <t>Welkin_Moon</t>
         </is>
       </c>
+      <c r="G661" s="13" t="inlineStr">
+        <is>
+          <t>35(10)</t>
+        </is>
+      </c>
     </row>
     <row r="662">
       <c r="A662" s="7" t="n"/>
@@ -17783,6 +20102,11 @@
           <t>Pilameda_City</t>
         </is>
       </c>
+      <c r="G662" s="13" t="inlineStr">
+        <is>
+          <t>2111(25)</t>
+        </is>
+      </c>
     </row>
     <row r="663">
       <c r="A663" s="7" t="n"/>
@@ -17809,6 +20133,11 @@
           <t>Frost_Moon_Factory</t>
         </is>
       </c>
+      <c r="G663" s="13" t="inlineStr">
+        <is>
+          <t>100(20)</t>
+        </is>
+      </c>
     </row>
     <row r="664">
       <c r="A664" s="7" t="n"/>
@@ -17835,6 +20164,11 @@
           <t>Pyroland</t>
         </is>
       </c>
+      <c r="G664" s="13" t="inlineStr">
+        <is>
+          <t>902(5)</t>
+        </is>
+      </c>
     </row>
     <row r="665">
       <c r="A665" s="7" t="n"/>
@@ -17861,6 +20195,11 @@
           <t>Nothing_Passage</t>
         </is>
       </c>
+      <c r="G665" s="13" t="inlineStr">
+        <is>
+          <t>1439(10)</t>
+        </is>
+      </c>
     </row>
     <row r="666">
       <c r="A666" s="7" t="n"/>
@@ -17887,6 +20226,11 @@
           <t>Blue_Amber_Lake</t>
         </is>
       </c>
+      <c r="G666" s="13" t="inlineStr">
+        <is>
+          <t>11396(15)</t>
+        </is>
+      </c>
     </row>
     <row r="667">
       <c r="A667" s="7" t="n"/>
@@ -17913,6 +20257,11 @@
           <t>Krumkake_Craftshop</t>
         </is>
       </c>
+      <c r="G667" s="13" t="inlineStr">
+        <is>
+          <t>2512(10)</t>
+        </is>
+      </c>
     </row>
     <row r="668">
       <c r="A668" s="7" t="n"/>
@@ -17939,6 +20288,7 @@
           <t>Welkin_Moon</t>
         </is>
       </c>
+      <c r="G668" s="13" t="inlineStr"/>
     </row>
     <row r="669">
       <c r="A669" s="7" t="n"/>
@@ -17965,6 +20315,11 @@
           <t>Welkin_Moon</t>
         </is>
       </c>
+      <c r="G669" s="13" t="inlineStr">
+        <is>
+          <t>500(10)</t>
+        </is>
+      </c>
     </row>
     <row r="670">
       <c r="A670" s="7" t="n"/>
@@ -17991,6 +20346,11 @@
           <t>Welkin_Moon</t>
         </is>
       </c>
+      <c r="G670" s="13" t="inlineStr">
+        <is>
+          <t>184(10)</t>
+        </is>
+      </c>
     </row>
     <row r="671">
       <c r="A671" s="7" t="n"/>
@@ -18017,6 +20377,7 @@
           <t>Cryoland</t>
         </is>
       </c>
+      <c r="G671" s="13" t="inlineStr"/>
     </row>
     <row r="672">
       <c r="A672" s="8" t="n"/>
@@ -18043,6 +20404,7 @@
           <t>Welkin_Moon</t>
         </is>
       </c>
+      <c r="G672" s="13" t="inlineStr"/>
     </row>
     <row r="673">
       <c r="A673" s="2" t="inlineStr">
@@ -18073,6 +20435,7 @@
           <t>Cryoland</t>
         </is>
       </c>
+      <c r="G673" s="13" t="inlineStr"/>
     </row>
     <row r="674">
       <c r="A674" s="7" t="n"/>
@@ -18099,6 +20462,7 @@
           <t>Cryoland</t>
         </is>
       </c>
+      <c r="G674" s="13" t="inlineStr"/>
     </row>
     <row r="675">
       <c r="A675" s="7" t="n"/>
@@ -18125,6 +20489,7 @@
           <t>Cryoland</t>
         </is>
       </c>
+      <c r="G675" s="13" t="inlineStr"/>
     </row>
     <row r="676">
       <c r="A676" s="7" t="n"/>
@@ -18151,6 +20516,7 @@
           <t>Cryoland</t>
         </is>
       </c>
+      <c r="G676" s="13" t="inlineStr"/>
     </row>
     <row r="677">
       <c r="A677" s="7" t="n"/>
@@ -18177,6 +20543,7 @@
           <t>Cryoland</t>
         </is>
       </c>
+      <c r="G677" s="13" t="inlineStr"/>
     </row>
     <row r="678">
       <c r="A678" s="7" t="n"/>
@@ -18203,6 +20570,7 @@
           <t>Cryoland</t>
         </is>
       </c>
+      <c r="G678" s="13" t="inlineStr"/>
     </row>
     <row r="679">
       <c r="A679" s="7" t="n"/>
@@ -18229,6 +20597,7 @@
           <t>Cryoland</t>
         </is>
       </c>
+      <c r="G679" s="13" t="inlineStr"/>
     </row>
     <row r="680">
       <c r="A680" s="7" t="n"/>
@@ -18255,6 +20624,7 @@
           <t>Cryoland</t>
         </is>
       </c>
+      <c r="G680" s="13" t="inlineStr"/>
     </row>
     <row r="681">
       <c r="A681" s="7" t="n"/>
@@ -18281,6 +20651,7 @@
           <t>Cryoland</t>
         </is>
       </c>
+      <c r="G681" s="13" t="inlineStr"/>
     </row>
     <row r="682">
       <c r="A682" s="7" t="n"/>
@@ -18307,6 +20678,7 @@
           <t>Cryoland</t>
         </is>
       </c>
+      <c r="G682" s="13" t="inlineStr"/>
     </row>
     <row r="683">
       <c r="A683" s="7" t="n"/>
@@ -18333,6 +20705,7 @@
           <t>Cryoland</t>
         </is>
       </c>
+      <c r="G683" s="13" t="inlineStr"/>
     </row>
     <row r="684">
       <c r="A684" s="7" t="n"/>
@@ -18359,6 +20732,7 @@
           <t>Cryoland</t>
         </is>
       </c>
+      <c r="G684" s="13" t="inlineStr"/>
     </row>
     <row r="685">
       <c r="A685" s="7" t="n"/>
@@ -18385,6 +20759,7 @@
           <t>Cryoland</t>
         </is>
       </c>
+      <c r="G685" s="13" t="inlineStr"/>
     </row>
     <row r="686">
       <c r="A686" s="7" t="n"/>
@@ -18411,6 +20786,7 @@
           <t>Cryoland</t>
         </is>
       </c>
+      <c r="G686" s="13" t="inlineStr"/>
     </row>
     <row r="687">
       <c r="A687" s="7" t="n"/>
@@ -18437,6 +20813,7 @@
           <t>Cryoland</t>
         </is>
       </c>
+      <c r="G687" s="13" t="inlineStr"/>
     </row>
     <row r="688">
       <c r="A688" s="7" t="n"/>
@@ -18463,6 +20840,7 @@
           <t>Cryoland</t>
         </is>
       </c>
+      <c r="G688" s="13" t="inlineStr"/>
     </row>
     <row r="689">
       <c r="A689" s="7" t="n"/>
@@ -18489,6 +20867,7 @@
           <t>Cryoland</t>
         </is>
       </c>
+      <c r="G689" s="13" t="inlineStr"/>
     </row>
     <row r="690">
       <c r="A690" s="7" t="n"/>
@@ -18515,6 +20894,7 @@
           <t>Cryoland</t>
         </is>
       </c>
+      <c r="G690" s="13" t="inlineStr"/>
     </row>
     <row r="691">
       <c r="A691" s="7" t="n"/>
@@ -18541,6 +20921,7 @@
           <t>Cryoland</t>
         </is>
       </c>
+      <c r="G691" s="13" t="inlineStr"/>
     </row>
     <row r="692">
       <c r="A692" s="7" t="n"/>
@@ -18567,6 +20948,7 @@
           <t>Cryoland</t>
         </is>
       </c>
+      <c r="G692" s="13" t="inlineStr"/>
     </row>
     <row r="693">
       <c r="A693" s="7" t="n"/>
@@ -18593,6 +20975,7 @@
           <t>Cryoland</t>
         </is>
       </c>
+      <c r="G693" s="13" t="inlineStr"/>
     </row>
     <row r="694">
       <c r="A694" s="7" t="n"/>
@@ -18619,6 +21002,7 @@
           <t>Cryoland</t>
         </is>
       </c>
+      <c r="G694" s="13" t="inlineStr"/>
     </row>
     <row r="695">
       <c r="A695" s="7" t="n"/>
@@ -18645,6 +21029,7 @@
           <t>Cryoland</t>
         </is>
       </c>
+      <c r="G695" s="13" t="inlineStr"/>
     </row>
     <row r="696">
       <c r="A696" s="7" t="n"/>
@@ -18671,6 +21056,7 @@
           <t>Cryoland</t>
         </is>
       </c>
+      <c r="G696" s="13" t="inlineStr"/>
     </row>
     <row r="697">
       <c r="A697" s="7" t="n"/>
@@ -18697,6 +21083,7 @@
           <t>Cryoland</t>
         </is>
       </c>
+      <c r="G697" s="13" t="inlineStr"/>
     </row>
     <row r="698">
       <c r="A698" s="7" t="n"/>
@@ -18723,6 +21110,7 @@
           <t>Cryoland</t>
         </is>
       </c>
+      <c r="G698" s="13" t="inlineStr"/>
     </row>
     <row r="699">
       <c r="A699" s="7" t="n"/>
@@ -18749,6 +21137,7 @@
           <t>Cryoland</t>
         </is>
       </c>
+      <c r="G699" s="13" t="inlineStr"/>
     </row>
     <row r="700">
       <c r="A700" s="7" t="n"/>
@@ -18775,6 +21164,7 @@
           <t>Cryoland</t>
         </is>
       </c>
+      <c r="G700" s="13" t="inlineStr"/>
     </row>
     <row r="701">
       <c r="A701" s="7" t="n"/>
@@ -18801,6 +21191,7 @@
           <t>Cryoland</t>
         </is>
       </c>
+      <c r="G701" s="13" t="inlineStr"/>
     </row>
     <row r="702">
       <c r="A702" s="7" t="n"/>
@@ -18827,6 +21218,11 @@
           <t>Snezhnaya_Palace</t>
         </is>
       </c>
+      <c r="G702" s="13" t="inlineStr">
+        <is>
+          <t>220(100)</t>
+        </is>
+      </c>
     </row>
     <row r="703">
       <c r="A703" s="7" t="n"/>
@@ -18853,6 +21249,7 @@
           <t>Cryoland</t>
         </is>
       </c>
+      <c r="G703" s="13" t="inlineStr"/>
     </row>
     <row r="704">
       <c r="A704" s="7" t="n"/>
@@ -18879,6 +21276,7 @@
           <t>Cryoland</t>
         </is>
       </c>
+      <c r="G704" s="13" t="inlineStr"/>
     </row>
     <row r="705">
       <c r="A705" s="7" t="n"/>
@@ -18905,6 +21303,7 @@
           <t>Cryoland</t>
         </is>
       </c>
+      <c r="G705" s="13" t="inlineStr"/>
     </row>
     <row r="706">
       <c r="A706" s="7" t="n"/>
@@ -18931,6 +21330,7 @@
           <t>Cryoland</t>
         </is>
       </c>
+      <c r="G706" s="13" t="inlineStr"/>
     </row>
     <row r="707">
       <c r="A707" s="7" t="n"/>
@@ -18957,6 +21357,7 @@
           <t>Cryoland</t>
         </is>
       </c>
+      <c r="G707" s="13" t="inlineStr"/>
     </row>
     <row r="708">
       <c r="A708" s="7" t="n"/>
@@ -18983,6 +21384,7 @@
           <t>Cryoland</t>
         </is>
       </c>
+      <c r="G708" s="13" t="inlineStr"/>
     </row>
     <row r="709">
       <c r="A709" s="7" t="n"/>
@@ -19009,6 +21411,7 @@
           <t>Cryoland</t>
         </is>
       </c>
+      <c r="G709" s="13" t="inlineStr"/>
     </row>
     <row r="710">
       <c r="A710" s="7" t="n"/>
@@ -19035,6 +21438,7 @@
           <t>Cryoland</t>
         </is>
       </c>
+      <c r="G710" s="13" t="inlineStr"/>
     </row>
     <row r="711">
       <c r="A711" s="7" t="n"/>
@@ -19061,6 +21465,7 @@
           <t>Cryoland</t>
         </is>
       </c>
+      <c r="G711" s="13" t="inlineStr"/>
     </row>
     <row r="712">
       <c r="A712" s="7" t="n"/>
@@ -19087,6 +21492,7 @@
           <t>Cryoland</t>
         </is>
       </c>
+      <c r="G712" s="13" t="inlineStr"/>
     </row>
     <row r="713">
       <c r="A713" s="8" t="n"/>
@@ -19113,6 +21519,7 @@
           <t>Cryoland</t>
         </is>
       </c>
+      <c r="G713" s="13" t="inlineStr"/>
     </row>
     <row r="714">
       <c r="A714" s="2" t="inlineStr">
@@ -19141,6 +21548,11 @@
       <c r="F714" s="6" t="inlineStr">
         <is>
           <t>GUN_QQ_Land1</t>
+        </is>
+      </c>
+      <c r="G714" s="13" t="inlineStr">
+        <is>
+          <t>3717(5)</t>
         </is>
       </c>
     </row>
@@ -19169,6 +21581,11 @@
           <t>GUN_Lion_Town2</t>
         </is>
       </c>
+      <c r="G715" s="13" t="inlineStr">
+        <is>
+          <t>3740(5)</t>
+        </is>
+      </c>
     </row>
     <row r="716">
       <c r="A716" s="7" t="n"/>
@@ -19195,6 +21612,7 @@
           <t>death</t>
         </is>
       </c>
+      <c r="G716" s="13" t="inlineStr"/>
     </row>
     <row r="717">
       <c r="A717" s="7" t="n"/>
@@ -19221,6 +21639,11 @@
           <t>Musk_Reef</t>
         </is>
       </c>
+      <c r="G717" s="13" t="inlineStr">
+        <is>
+          <t>1023(10)</t>
+        </is>
+      </c>
     </row>
     <row r="718">
       <c r="A718" s="7" t="n"/>
@@ -19247,6 +21670,7 @@
           <t>Abyssland</t>
         </is>
       </c>
+      <c r="G718" s="13" t="inlineStr"/>
     </row>
     <row r="719">
       <c r="A719" s="7" t="n"/>
@@ -19273,6 +21697,7 @@
           <t>Abyssland</t>
         </is>
       </c>
+      <c r="G719" s="13" t="inlineStr"/>
     </row>
     <row r="720">
       <c r="A720" s="7" t="n"/>
@@ -19299,6 +21724,7 @@
           <t>Abyssland</t>
         </is>
       </c>
+      <c r="G720" s="13" t="inlineStr"/>
     </row>
     <row r="721">
       <c r="A721" s="7" t="n"/>
@@ -19325,6 +21751,7 @@
           <t>Abyssland</t>
         </is>
       </c>
+      <c r="G721" s="13" t="inlineStr"/>
     </row>
     <row r="722">
       <c r="A722" s="7" t="n"/>
@@ -19351,6 +21778,7 @@
           <t>Abyssland</t>
         </is>
       </c>
+      <c r="G722" s="13" t="inlineStr"/>
     </row>
     <row r="723">
       <c r="A723" s="7" t="n"/>
@@ -19377,6 +21805,11 @@
           <t>Twin_Island</t>
         </is>
       </c>
+      <c r="G723" s="13" t="inlineStr">
+        <is>
+          <t>2259(10)</t>
+        </is>
+      </c>
     </row>
     <row r="724">
       <c r="A724" s="7" t="n"/>
@@ -19403,6 +21836,11 @@
           <t>Golden_Apple_Islands</t>
         </is>
       </c>
+      <c r="G724" s="13" t="inlineStr">
+        <is>
+          <t>3861(10)</t>
+        </is>
+      </c>
     </row>
     <row r="725">
       <c r="A725" s="7" t="n"/>
@@ -19429,6 +21867,7 @@
           <t>Abyssland</t>
         </is>
       </c>
+      <c r="G725" s="13" t="inlineStr"/>
     </row>
     <row r="726">
       <c r="A726" s="7" t="n"/>
@@ -19455,6 +21894,7 @@
           <t>Abyssland</t>
         </is>
       </c>
+      <c r="G726" s="13" t="inlineStr"/>
     </row>
     <row r="727">
       <c r="A727" s="7" t="n"/>
@@ -19481,6 +21921,11 @@
           <t>Pudding_Island</t>
         </is>
       </c>
+      <c r="G727" s="13" t="inlineStr">
+        <is>
+          <t>4003(10)</t>
+        </is>
+      </c>
     </row>
     <row r="728">
       <c r="A728" s="7" t="n"/>
@@ -19507,6 +21952,7 @@
           <t>Abyssland</t>
         </is>
       </c>
+      <c r="G728" s="13" t="inlineStr"/>
     </row>
     <row r="729">
       <c r="A729" s="7" t="n"/>
@@ -19533,6 +21979,11 @@
           <t>Broken_Island</t>
         </is>
       </c>
+      <c r="G729" s="13" t="inlineStr">
+        <is>
+          <t>3810(10)</t>
+        </is>
+      </c>
     </row>
     <row r="730">
       <c r="A730" s="7" t="n"/>
@@ -19559,6 +22010,11 @@
           <t>Danger_Island</t>
         </is>
       </c>
+      <c r="G730" s="13" t="inlineStr">
+        <is>
+          <t>4122(10)</t>
+        </is>
+      </c>
     </row>
     <row r="731">
       <c r="A731" s="7" t="n"/>
@@ -19585,6 +22041,11 @@
           <t>Heavenland</t>
         </is>
       </c>
+      <c r="G731" s="13" t="inlineStr">
+        <is>
+          <t>869(100)</t>
+        </is>
+      </c>
     </row>
     <row r="732">
       <c r="A732" s="7" t="n"/>
@@ -19611,6 +22072,7 @@
           <t>Heavenland</t>
         </is>
       </c>
+      <c r="G732" s="13" t="inlineStr"/>
     </row>
     <row r="733">
       <c r="A733" s="7" t="n"/>
@@ -19637,6 +22099,7 @@
           <t>Heavenland</t>
         </is>
       </c>
+      <c r="G733" s="13" t="inlineStr"/>
     </row>
     <row r="734">
       <c r="A734" s="7" t="n"/>
@@ -19663,6 +22126,7 @@
           <t>Heavenland</t>
         </is>
       </c>
+      <c r="G734" s="13" t="inlineStr"/>
     </row>
     <row r="735">
       <c r="A735" s="7" t="n"/>
@@ -19689,6 +22153,7 @@
           <t>Heavenland</t>
         </is>
       </c>
+      <c r="G735" s="13" t="inlineStr"/>
     </row>
     <row r="736">
       <c r="A736" s="7" t="n"/>
@@ -19715,6 +22180,7 @@
           <t>space</t>
         </is>
       </c>
+      <c r="G736" s="13" t="inlineStr"/>
     </row>
     <row r="737">
       <c r="A737" s="7" t="n"/>
@@ -19741,6 +22207,7 @@
           <t>exist</t>
         </is>
       </c>
+      <c r="G737" s="13" t="inlineStr"/>
     </row>
     <row r="738">
       <c r="A738" s="7" t="n"/>
@@ -19767,6 +22234,7 @@
           <t>time</t>
         </is>
       </c>
+      <c r="G738" s="13" t="inlineStr"/>
     </row>
     <row r="739">
       <c r="A739" s="7" t="n"/>
@@ -19793,6 +22261,7 @@
           <t>world</t>
         </is>
       </c>
+      <c r="G739" s="13" t="inlineStr"/>
     </row>
     <row r="740">
       <c r="A740" s="7" t="n"/>
@@ -19819,6 +22288,7 @@
           <t>did</t>
         </is>
       </c>
+      <c r="G740" s="13" t="inlineStr"/>
     </row>
     <row r="741">
       <c r="A741" s="8" t="n"/>
@@ -19845,8 +22315,10 @@
           <t>Heavenland</t>
         </is>
       </c>
+      <c r="G741" s="13" t="inlineStr"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:G741"/>
   <mergeCells count="9">
     <mergeCell ref="A346:A497"/>
     <mergeCell ref="A254:A345"/>
@@ -33654,8 +36126,8 @@
     <mergeCell ref="A429:A447"/>
     <mergeCell ref="A99:A104"/>
     <mergeCell ref="A448:A464"/>
+    <mergeCell ref="B673:B713"/>
     <mergeCell ref="B29:B34"/>
-    <mergeCell ref="B673:B713"/>
     <mergeCell ref="B96:B98"/>
     <mergeCell ref="C673:C713"/>
     <mergeCell ref="A498:A623"/>
